--- a/01_raw_data/4.1_SOCS/raw/input/D2.2.CEN.AGRI.xlsx
+++ b/01_raw_data/4.1_SOCS/raw/input/D2.2.CEN.AGRI.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/bstacy_worldbank_org/Documents/DECIS/SPI/Data/SPI 2023/01_raw_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/zprinsloo_worldbank_org/Documents/spi/technical-work/SPI-Zander/SPI/01_raw_data/4.1_SOCS/raw/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="440" documentId="13_ncr:1_{3829F77E-C2E9-446E-AAA7-D7F1F56291B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AACA7F1-1E0C-44EB-B0DB-FB9657B6BE54}"/>
+  <xr:revisionPtr revIDLastSave="455" documentId="13_ncr:1_{3829F77E-C2E9-446E-AAA7-D7F1F56291B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2F99A55-3DC8-5C4E-9174-FE2403F48F15}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{88A39811-3C9E-4C6A-A624-06A0224B6123}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="1" activeTab="1" xr2:uid="{88A39811-3C9E-4C6A-A624-06A0224B6123}"/>
   </bookViews>
   <sheets>
     <sheet name="2020 DCS" sheetId="13" r:id="rId1"/>
     <sheet name="Data" sheetId="12" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data!$A$3:$AH$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data!$A$3:$AI$193</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -70,7 +70,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH15" authorId="0" shapeId="0" xr:uid="{42929CDE-F9C3-4A56-A6C4-2500E47E80B1}">
+    <comment ref="AI15" authorId="0" shapeId="0" xr:uid="{42929CDE-F9C3-4A56-A6C4-2500E47E80B1}">
       <text>
         <r>
           <rPr>
@@ -102,7 +102,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Aieshwarya Davis:</t>
         </r>
@@ -111,7 +111,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 No 2013 data available</t>
@@ -126,7 +126,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Aieshwarya Davis:</t>
         </r>
@@ -135,7 +135,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 No 2011 entry available  </t>
@@ -150,7 +150,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Aieshwarya Davis:</t>
         </r>
@@ -159,7 +159,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 No data for 2018
@@ -175,7 +175,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Aieshwarya Davis:</t>
         </r>
@@ -184,7 +184,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 NO 2006 data available</t>
@@ -199,7 +199,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Dereje Ketema Wolde:</t>
         </r>
@@ -208,7 +208,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 https://ask.rks-gov.net/en/kosovo-agency-of-statistics/agriculture/agriculture-census</t>
@@ -223,7 +223,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Aieshwarya Davis:</t>
         </r>
@@ -232,7 +232,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 no 2018 data available</t>
@@ -247,7 +247,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Dereje Ketema Wolde:</t>
         </r>
@@ -256,7 +256,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 http://www.nigerianstat.gov.ng/nada/index.php/catalog/15</t>
@@ -271,7 +271,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Dereje Ketema Wolde:</t>
         </r>
@@ -280,7 +280,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 https://www.gso.gov.vn/default_en.aspx?tabid=515&amp;idmid=5&amp;ItemID=8058</t>
@@ -295,6 +295,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Dereje Ketema Wolde:</t>
         </r>
@@ -303,6 +304,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Glossary:Farm_structure_survey_(FSS)</t>
@@ -317,6 +319,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Dereje Ketema Wolde:</t>
         </r>
@@ -325,6 +328,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Glossary:Farm_structure_survey_(FSS)</t>
@@ -339,6 +343,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Dereje Ketema Wolde:</t>
         </r>
@@ -347,6 +352,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Glossary:Farm_structure_survey_(FSS)</t>
@@ -361,6 +367,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Dereje Ketema Wolde:</t>
         </r>
@@ -369,6 +376,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Glossary:Farm_structure_survey_(FSS)</t>
@@ -383,6 +391,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Dereje Ketema Wolde:</t>
         </r>
@@ -391,6 +400,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 https://www.cbs.gov.il/en/mediarelease/pages/2020/national-agricultural-census-2017-crops.aspx</t>
@@ -405,6 +415,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>Dereje Ketema Wolde:</t>
         </r>
@@ -413,6 +424,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 https://ec.europa.eu/eurostat/statistics-explained/index.php/Glossary:Farm_structure_survey_(FSS)</t>
@@ -1705,7 +1717,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General_)"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1730,19 +1742,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1786,17 +1785,6 @@
       <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1891,106 +1879,106 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2018,9 +2006,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2058,7 +2046,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2164,7 +2152,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2306,7 +2294,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2315,12 +2303,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E312D5F-DF10-48EE-B97E-9DE14B8986B5}">
   <dimension ref="A1:AB192"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
         <v>0</v>
       </c>
@@ -2400,7 +2388,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -2411,7 +2399,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -2497,7 +2485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -2583,7 +2571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -2669,7 +2657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -2755,7 +2743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -2841,7 +2829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -2927,7 +2915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -3013,7 +3001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -3099,7 +3087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -3185,7 +3173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -3271,7 +3259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -3357,7 +3345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -3443,7 +3431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -3529,7 +3517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -3615,7 +3603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:28">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -3701,7 +3689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -3787,7 +3775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:28">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -3873,7 +3861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:28">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -3959,7 +3947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:28">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -4045,7 +4033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:28">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -4131,7 +4119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:28">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -4217,7 +4205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:28">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -4303,7 +4291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:28">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -4389,7 +4377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:28">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -4475,7 +4463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:28">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -4561,7 +4549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:28">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -4647,7 +4635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:28">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -4733,7 +4721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:28">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -4819,7 +4807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:28">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>58</v>
       </c>
@@ -4905,7 +4893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:28">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>59</v>
       </c>
@@ -4991,7 +4979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:28">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>60</v>
       </c>
@@ -5077,7 +5065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:28">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>61</v>
       </c>
@@ -5163,7 +5151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:28">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>62</v>
       </c>
@@ -5249,7 +5237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:28">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>63</v>
       </c>
@@ -5335,7 +5323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:28">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>64</v>
       </c>
@@ -5421,7 +5409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:28">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -5507,7 +5495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:28">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>66</v>
       </c>
@@ -5593,7 +5581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:28">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>67</v>
       </c>
@@ -5679,7 +5667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:28">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>68</v>
       </c>
@@ -5765,7 +5753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:28">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>69</v>
       </c>
@@ -5851,7 +5839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:28">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>70</v>
       </c>
@@ -5937,7 +5925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:28">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>71</v>
       </c>
@@ -6023,7 +6011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:28">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>72</v>
       </c>
@@ -6109,7 +6097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:28">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>73</v>
       </c>
@@ -6195,7 +6183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:28">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>74</v>
       </c>
@@ -6281,7 +6269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:28">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>75</v>
       </c>
@@ -6367,7 +6355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:28">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>76</v>
       </c>
@@ -6453,7 +6441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:28">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -6539,7 +6527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:28">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>78</v>
       </c>
@@ -6625,7 +6613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:28">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>79</v>
       </c>
@@ -6711,7 +6699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:28">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -6797,7 +6785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:28">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>81</v>
       </c>
@@ -6883,7 +6871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:28">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -6969,7 +6957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:28">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -7055,7 +7043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:28">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>84</v>
       </c>
@@ -7141,7 +7129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:28">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>85</v>
       </c>
@@ -7227,7 +7215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:28">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>86</v>
       </c>
@@ -7313,7 +7301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:28">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>87</v>
       </c>
@@ -7399,7 +7387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:28">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>88</v>
       </c>
@@ -7485,7 +7473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:28">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>89</v>
       </c>
@@ -7571,7 +7559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:28">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>90</v>
       </c>
@@ -7657,7 +7645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:28">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>91</v>
       </c>
@@ -7743,7 +7731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:28">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>92</v>
       </c>
@@ -7829,7 +7817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:28">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>93</v>
       </c>
@@ -7915,7 +7903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:28">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>94</v>
       </c>
@@ -8001,7 +7989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:28">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>95</v>
       </c>
@@ -8087,7 +8075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:28">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>96</v>
       </c>
@@ -8173,7 +8161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:28">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>97</v>
       </c>
@@ -8259,7 +8247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:28">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>98</v>
       </c>
@@ -8345,7 +8333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:28">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>99</v>
       </c>
@@ -8431,7 +8419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:28">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>100</v>
       </c>
@@ -8517,7 +8505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:28">
+    <row r="74" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>101</v>
       </c>
@@ -8603,7 +8591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:28">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>102</v>
       </c>
@@ -8689,7 +8677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:28">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>103</v>
       </c>
@@ -8775,7 +8763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:28">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>104</v>
       </c>
@@ -8861,7 +8849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:28">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>105</v>
       </c>
@@ -8947,7 +8935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:28">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>106</v>
       </c>
@@ -9033,7 +9021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:28">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>107</v>
       </c>
@@ -9119,7 +9107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:28">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>108</v>
       </c>
@@ -9205,7 +9193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:28">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>109</v>
       </c>
@@ -9291,7 +9279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:28">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>110</v>
       </c>
@@ -9377,7 +9365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:28">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>111</v>
       </c>
@@ -9463,7 +9451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:28">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>112</v>
       </c>
@@ -9549,7 +9537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:28">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>113</v>
       </c>
@@ -9635,7 +9623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:28">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>114</v>
       </c>
@@ -9721,7 +9709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:28">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>115</v>
       </c>
@@ -9807,7 +9795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:28">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>116</v>
       </c>
@@ -9893,7 +9881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:28">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>117</v>
       </c>
@@ -9979,7 +9967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:28">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>118</v>
       </c>
@@ -10065,7 +10053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:28">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>119</v>
       </c>
@@ -10151,7 +10139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:28">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>120</v>
       </c>
@@ -10237,7 +10225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:28">
+    <row r="94" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>121</v>
       </c>
@@ -10323,7 +10311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:28">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>122</v>
       </c>
@@ -10409,7 +10397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:28">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>123</v>
       </c>
@@ -10495,7 +10483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:28">
+    <row r="97" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>124</v>
       </c>
@@ -10581,7 +10569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:28">
+    <row r="98" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>125</v>
       </c>
@@ -10667,7 +10655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:28">
+    <row r="99" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>126</v>
       </c>
@@ -10753,7 +10741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:28">
+    <row r="100" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>127</v>
       </c>
@@ -10839,7 +10827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:28">
+    <row r="101" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>128</v>
       </c>
@@ -10925,7 +10913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:28">
+    <row r="102" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>129</v>
       </c>
@@ -11011,7 +10999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:28">
+    <row r="103" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>130</v>
       </c>
@@ -11097,7 +11085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:28">
+    <row r="104" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>131</v>
       </c>
@@ -11183,7 +11171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:28">
+    <row r="105" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>132</v>
       </c>
@@ -11269,7 +11257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:28">
+    <row r="106" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>133</v>
       </c>
@@ -11355,7 +11343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:28">
+    <row r="107" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>134</v>
       </c>
@@ -11441,7 +11429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:28">
+    <row r="108" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>135</v>
       </c>
@@ -11527,7 +11515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:28">
+    <row r="109" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>136</v>
       </c>
@@ -11613,7 +11601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:28">
+    <row r="110" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>137</v>
       </c>
@@ -11699,7 +11687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:28">
+    <row r="111" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>138</v>
       </c>
@@ -11785,7 +11773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:28">
+    <row r="112" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>139</v>
       </c>
@@ -11871,7 +11859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28">
+    <row r="113" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>140</v>
       </c>
@@ -11957,7 +11945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28">
+    <row r="114" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>141</v>
       </c>
@@ -12043,7 +12031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:28">
+    <row r="115" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>142</v>
       </c>
@@ -12129,7 +12117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28">
+    <row r="116" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>143</v>
       </c>
@@ -12215,7 +12203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>144</v>
       </c>
@@ -12301,7 +12289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>145</v>
       </c>
@@ -12387,7 +12375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28">
+    <row r="119" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>146</v>
       </c>
@@ -12473,7 +12461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28">
+    <row r="120" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>147</v>
       </c>
@@ -12559,7 +12547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28">
+    <row r="121" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>148</v>
       </c>
@@ -12645,7 +12633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28">
+    <row r="122" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>149</v>
       </c>
@@ -12731,7 +12719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28">
+    <row r="123" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>150</v>
       </c>
@@ -12817,7 +12805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:28">
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>151</v>
       </c>
@@ -12903,7 +12891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:28">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>152</v>
       </c>
@@ -12989,7 +12977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:28">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>153</v>
       </c>
@@ -13075,7 +13063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:28">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>154</v>
       </c>
@@ -13161,7 +13149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:28">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>155</v>
       </c>
@@ -13247,7 +13235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:28">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>156</v>
       </c>
@@ -13333,7 +13321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:28">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>157</v>
       </c>
@@ -13419,7 +13407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:28">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>158</v>
       </c>
@@ -13505,7 +13493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:28">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>159</v>
       </c>
@@ -13591,7 +13579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:28">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>160</v>
       </c>
@@ -13677,7 +13665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:28">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>161</v>
       </c>
@@ -13763,7 +13751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:28">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>162</v>
       </c>
@@ -13849,7 +13837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:28">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>163</v>
       </c>
@@ -13935,7 +13923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:28">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>164</v>
       </c>
@@ -14021,7 +14009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:28">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>165</v>
       </c>
@@ -14107,7 +14095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:28">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>166</v>
       </c>
@@ -14193,7 +14181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:28">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>167</v>
       </c>
@@ -14279,7 +14267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:28">
+    <row r="141" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>168</v>
       </c>
@@ -14365,7 +14353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:28">
+    <row r="142" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>169</v>
       </c>
@@ -14451,7 +14439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:28">
+    <row r="143" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>170</v>
       </c>
@@ -14537,7 +14525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:28">
+    <row r="144" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>171</v>
       </c>
@@ -14623,7 +14611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:28">
+    <row r="145" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>172</v>
       </c>
@@ -14709,7 +14697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:28">
+    <row r="146" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>173</v>
       </c>
@@ -14795,7 +14783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:28">
+    <row r="147" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>174</v>
       </c>
@@ -14881,7 +14869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:28">
+    <row r="148" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>175</v>
       </c>
@@ -14967,7 +14955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:28">
+    <row r="149" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>176</v>
       </c>
@@ -15053,7 +15041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:28">
+    <row r="150" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>177</v>
       </c>
@@ -15139,7 +15127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:28">
+    <row r="151" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>178</v>
       </c>
@@ -15225,7 +15213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:28">
+    <row r="152" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>179</v>
       </c>
@@ -15311,7 +15299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:28">
+    <row r="153" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>180</v>
       </c>
@@ -15397,7 +15385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:28">
+    <row r="154" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>181</v>
       </c>
@@ -15483,7 +15471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:28">
+    <row r="155" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>182</v>
       </c>
@@ -15569,7 +15557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:28">
+    <row r="156" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>183</v>
       </c>
@@ -15655,7 +15643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:28">
+    <row r="157" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>184</v>
       </c>
@@ -15741,7 +15729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:28">
+    <row r="158" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>185</v>
       </c>
@@ -15827,7 +15815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:28">
+    <row r="159" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>186</v>
       </c>
@@ -15913,7 +15901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:28">
+    <row r="160" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>187</v>
       </c>
@@ -15999,7 +15987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:28">
+    <row r="161" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>188</v>
       </c>
@@ -16085,7 +16073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:28">
+    <row r="162" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>189</v>
       </c>
@@ -16171,7 +16159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:28">
+    <row r="163" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>190</v>
       </c>
@@ -16257,7 +16245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:28">
+    <row r="164" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>191</v>
       </c>
@@ -16343,7 +16331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:28">
+    <row r="165" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>192</v>
       </c>
@@ -16429,7 +16417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:28">
+    <row r="166" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>193</v>
       </c>
@@ -16515,7 +16503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:28">
+    <row r="167" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>194</v>
       </c>
@@ -16601,7 +16589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:28">
+    <row r="168" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>195</v>
       </c>
@@ -16687,7 +16675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:28">
+    <row r="169" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>196</v>
       </c>
@@ -16773,7 +16761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:28">
+    <row r="170" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>197</v>
       </c>
@@ -16859,7 +16847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:28">
+    <row r="171" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>198</v>
       </c>
@@ -16945,7 +16933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:28">
+    <row r="172" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>199</v>
       </c>
@@ -17031,7 +17019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:28">
+    <row r="173" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>200</v>
       </c>
@@ -17117,7 +17105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:28">
+    <row r="174" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>201</v>
       </c>
@@ -17203,7 +17191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:28">
+    <row r="175" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>202</v>
       </c>
@@ -17289,7 +17277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:28">
+    <row r="176" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>203</v>
       </c>
@@ -17375,7 +17363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:28">
+    <row r="177" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>204</v>
       </c>
@@ -17461,7 +17449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:28">
+    <row r="178" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>205</v>
       </c>
@@ -17547,7 +17535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:28">
+    <row r="179" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>206</v>
       </c>
@@ -17633,7 +17621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:28">
+    <row r="180" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>207</v>
       </c>
@@ -17719,7 +17707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:28">
+    <row r="181" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>208</v>
       </c>
@@ -17805,7 +17793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:28">
+    <row r="182" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>209</v>
       </c>
@@ -17891,7 +17879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:28">
+    <row r="183" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>210</v>
       </c>
@@ -17977,7 +17965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:28">
+    <row r="184" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>211</v>
       </c>
@@ -18063,7 +18051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:28">
+    <row r="185" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>212</v>
       </c>
@@ -18149,7 +18137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:28">
+    <row r="186" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>213</v>
       </c>
@@ -18235,7 +18223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:28">
+    <row r="187" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>214</v>
       </c>
@@ -18321,7 +18309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:28">
+    <row r="188" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>215</v>
       </c>
@@ -18407,7 +18395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:28">
+    <row r="189" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>216</v>
       </c>
@@ -18493,7 +18481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:28">
+    <row r="190" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>217</v>
       </c>
@@ -18579,7 +18567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:28">
+    <row r="191" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>218</v>
       </c>
@@ -18665,7 +18653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:28">
+    <row r="192" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>219</v>
       </c>
@@ -18752,34 +18740,37 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Official Use Only</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{864920DE-DFEB-4690-A75E-6A3FFD9E47FC}">
-  <dimension ref="A1:AJ193"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AK193"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.5703125" style="5" customWidth="1"/>
-    <col min="6" max="9" width="9.140625" style="9"/>
+    <col min="1" max="1" width="5.1640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.5" style="5" customWidth="1"/>
+    <col min="6" max="9" width="9.1640625" style="9"/>
     <col min="10" max="10" width="12" style="9" customWidth="1"/>
-    <col min="11" max="24" width="9.140625" style="9"/>
-    <col min="25" max="25" width="16.85546875" style="9" customWidth="1"/>
-    <col min="26" max="30" width="9.140625" style="9"/>
-    <col min="31" max="32" width="9.42578125" style="9" customWidth="1"/>
-    <col min="33" max="33" width="44.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="24.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="17.5703125" style="9" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="9"/>
+    <col min="11" max="24" width="9.1640625" style="9"/>
+    <col min="25" max="25" width="16.83203125" style="9" customWidth="1"/>
+    <col min="26" max="30" width="9.1640625" style="9"/>
+    <col min="31" max="33" width="9.5" style="9" customWidth="1"/>
+    <col min="34" max="34" width="44.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="24.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="17.5" style="9" customWidth="1"/>
+    <col min="37" max="16384" width="9.1640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C1" s="9"/>
       <c r="D1" s="6" t="s">
         <v>220</v>
@@ -18796,11 +18787,11 @@
       <c r="Y1" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="AH1" s="9" t="s">
+      <c r="AI1" s="9" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B2" s="5">
         <v>1</v>
       </c>
@@ -18886,8 +18877,9 @@
       <c r="AD2" s="5"/>
       <c r="AE2" s="5"/>
       <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>225</v>
       </c>
@@ -19005,14 +18997,17 @@
       <c r="AF3" s="38">
         <v>2024</v>
       </c>
-      <c r="AG3" s="12" t="s">
+      <c r="AG3" s="38">
+        <v>2025</v>
+      </c>
+      <c r="AH3" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="AH3" s="36" t="s">
+      <c r="AI3" s="36" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>1</v>
       </c>
@@ -19101,18 +19096,19 @@
       <c r="AD4" s="12"/>
       <c r="AE4" s="12"/>
       <c r="AF4" s="12"/>
-      <c r="AG4" s="12" t="str">
-        <f>+IF($D4=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E4=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F4=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G4=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H4=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I4=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J4=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K4=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L4=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M4=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N4=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O4=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P4=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q4=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R4=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S4=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T4=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U4=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V4=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W4=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X4=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y4=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z4=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA4=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB4=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC4=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD4=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE4=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF4=1, RIGHT(AF$3,4)&amp;", ", "")</f>
+      <c r="AG4" s="12"/>
+      <c r="AH4" s="12" t="str">
+        <f>+IF($D4=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E4=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F4=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G4=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H4=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I4=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J4=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K4=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L4=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M4=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N4=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O4=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P4=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q4=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R4=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S4=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T4=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U4=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V4=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W4=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X4=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y4=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z4=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA4=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB4=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC4=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD4=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE4=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF4=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG4=1, RIGHT(AG$3,4)&amp;", ", "")</f>
         <v xml:space="preserve">2003, </v>
       </c>
-      <c r="AH4" s="37" t="s">
+      <c r="AI4" s="37" t="s">
         <v>228</v>
       </c>
-      <c r="AI4" s="42" t="s">
+      <c r="AJ4" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <f t="shared" ref="A5:A68" si="1">1+A4</f>
         <v>2</v>
@@ -19202,18 +19198,19 @@
       <c r="AD5" s="12"/>
       <c r="AE5" s="12"/>
       <c r="AF5" s="12"/>
-      <c r="AG5" s="12" t="str">
-        <f t="shared" ref="AG4:AG67" si="2">+IF($D5=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E5=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F5=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G5=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H5=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I5=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J5=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K5=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L5=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M5=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N5=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O5=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P5=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q5=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R5=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S5=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T5=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U5=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V5=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W5=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X5=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y5=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z5=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA5=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB5=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC5=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD5=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE5=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF5=1, RIGHT(AF$3,4)&amp;", ", "")</f>
+      <c r="AG5" s="12"/>
+      <c r="AH5" s="12" t="str">
+        <f>+IF($D5=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E5=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F5=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G5=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H5=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I5=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J5=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K5=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L5=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M5=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N5=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O5=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P5=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q5=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R5=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S5=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T5=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U5=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V5=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W5=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X5=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y5=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z5=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA5=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB5=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC5=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD5=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE5=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF5=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG5=1, RIGHT(AG$3,4)&amp;", ", "")</f>
         <v xml:space="preserve">1998, 2012, 2020, </v>
       </c>
-      <c r="AH5" s="37" t="s">
+      <c r="AI5" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="AI5" s="42" t="s">
+      <c r="AJ5" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -19303,18 +19300,19 @@
       <c r="AD6" s="12"/>
       <c r="AE6" s="12"/>
       <c r="AF6" s="12"/>
-      <c r="AG6" s="12" t="str">
-        <f t="shared" si="2"/>
+      <c r="AG6" s="12"/>
+      <c r="AH6" s="12" t="str">
+        <f>+IF($D6=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E6=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F6=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G6=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H6=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I6=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J6=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K6=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L6=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M6=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N6=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O6=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P6=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q6=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R6=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S6=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T6=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U6=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V6=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W6=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X6=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y6=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z6=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA6=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB6=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC6=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD6=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE6=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF6=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG6=1, RIGHT(AG$3,4)&amp;", ", "")</f>
         <v xml:space="preserve">2001, </v>
       </c>
-      <c r="AH6" s="37" t="s">
+      <c r="AI6" s="37" t="s">
         <v>231</v>
       </c>
-      <c r="AI6" s="42" t="s">
+      <c r="AJ6" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -19406,18 +19404,19 @@
         <v>1</v>
       </c>
       <c r="AF7" s="12"/>
-      <c r="AG7" s="12" t="str">
-        <f t="shared" si="2"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12" t="str">
+        <f>+IF($D7=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E7=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F7=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G7=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H7=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I7=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J7=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K7=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L7=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M7=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N7=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O7=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P7=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q7=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R7=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S7=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T7=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U7=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V7=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W7=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X7=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y7=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z7=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA7=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB7=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC7=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD7=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE7=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF7=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG7=1, RIGHT(AG$3,4)&amp;", ", "")</f>
         <v xml:space="preserve">2019, 2023, </v>
       </c>
-      <c r="AH7" s="37" t="s">
+      <c r="AI7" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="AI7" s="42" t="s">
+      <c r="AJ7" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -19507,18 +19506,19 @@
       <c r="AD8" s="12"/>
       <c r="AE8" s="12"/>
       <c r="AF8" s="12"/>
-      <c r="AG8" s="12" t="str">
-        <f t="shared" si="2"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12" t="str">
+        <f t="shared" ref="AH8:AH71" si="2">+IF($D8=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E8=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F8=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G8=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H8=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I8=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J8=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K8=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L8=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M8=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N8=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O8=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P8=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q8=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R8=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S8=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T8=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U8=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V8=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W8=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X8=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y8=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z8=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA8=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB8=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC8=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD8=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE8=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF8=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG8=1, RIGHT(AG$3,4)&amp;", ", "")</f>
         <v xml:space="preserve">2001, 2007, </v>
       </c>
-      <c r="AH8" s="37" t="s">
+      <c r="AI8" s="37" t="s">
         <v>233</v>
       </c>
-      <c r="AI8" s="42" t="s">
+      <c r="AJ8" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -19608,18 +19608,19 @@
       <c r="AD9" s="12"/>
       <c r="AE9" s="12"/>
       <c r="AF9" s="12"/>
-      <c r="AG9" s="12" t="str">
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2002, 2008, 2018, </v>
       </c>
-      <c r="AH9" s="37" t="s">
+      <c r="AI9" s="37" t="s">
         <v>234</v>
       </c>
-      <c r="AI9" s="42" t="s">
+      <c r="AJ9" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -19709,18 +19710,19 @@
       <c r="AD10" s="12"/>
       <c r="AE10" s="12"/>
       <c r="AF10" s="12"/>
-      <c r="AG10" s="12" t="str">
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2014, </v>
       </c>
-      <c r="AH10" s="37" t="s">
+      <c r="AI10" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="AI10" s="42" t="s">
+      <c r="AJ10" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -19810,18 +19812,19 @@
       <c r="AD11" s="12"/>
       <c r="AE11" s="12"/>
       <c r="AF11" s="12"/>
-      <c r="AG11" s="12" t="str">
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2005, 2015, </v>
       </c>
-      <c r="AH11" s="37" t="s">
+      <c r="AI11" s="37" t="s">
         <v>236</v>
       </c>
-      <c r="AI11" s="42" t="s">
+      <c r="AJ11" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="1:35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -19911,18 +19914,19 @@
       <c r="AD12" s="12"/>
       <c r="AE12" s="12"/>
       <c r="AF12" s="12"/>
-      <c r="AG12" s="12" t="str">
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 2005, 2008, 2019, </v>
       </c>
-      <c r="AH12" s="37" t="s">
+      <c r="AI12" s="37" t="s">
         <v>237</v>
       </c>
-      <c r="AI12" s="42" t="s">
+      <c r="AJ12" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A13" s="13">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -20012,18 +20016,19 @@
       <c r="AD13" s="12"/>
       <c r="AE13" s="12"/>
       <c r="AF13" s="12"/>
-      <c r="AG13" s="12" t="str">
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2019, </v>
       </c>
-      <c r="AH13" s="37" t="s">
+      <c r="AI13" s="37" t="s">
         <v>238</v>
       </c>
-      <c r="AI13" s="42" t="s">
+      <c r="AJ13" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="14" spans="1:35">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" s="13">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -20113,18 +20118,19 @@
       <c r="AD14" s="12"/>
       <c r="AE14" s="12"/>
       <c r="AF14" s="12"/>
-      <c r="AG14" s="12" t="str">
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2011, 2018, </v>
       </c>
-      <c r="AH14" s="37" t="s">
+      <c r="AI14" s="37" t="s">
         <v>239</v>
       </c>
-      <c r="AI14" s="42" t="s">
+      <c r="AJ14" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="15" spans="1:35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" s="13">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -20214,18 +20220,19 @@
       <c r="AD15" s="12"/>
       <c r="AE15" s="12"/>
       <c r="AF15" s="12"/>
-      <c r="AG15" s="12" t="str">
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2019, </v>
       </c>
-      <c r="AH15" s="37" t="s">
+      <c r="AI15" s="37" t="s">
         <v>240</v>
       </c>
-      <c r="AI15" s="42" t="s">
+      <c r="AJ15" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:35">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" s="13">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -20315,18 +20322,19 @@
       <c r="AD16" s="12"/>
       <c r="AE16" s="12"/>
       <c r="AF16" s="12"/>
-      <c r="AG16" s="12" t="str">
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2000, 2009, 2019, </v>
       </c>
-      <c r="AH16" s="37" t="s">
+      <c r="AI16" s="37" t="s">
         <v>241</v>
       </c>
-      <c r="AI16" s="42" t="s">
+      <c r="AJ16" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="1:35">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A17" s="13">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -20416,18 +20424,19 @@
       <c r="AD17" s="12"/>
       <c r="AE17" s="12"/>
       <c r="AF17" s="12"/>
-      <c r="AG17" s="12" t="str">
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2013, </v>
       </c>
-      <c r="AH17" s="37" t="s">
+      <c r="AI17" s="37" t="s">
         <v>242</v>
       </c>
-      <c r="AI17" s="42" t="s">
+      <c r="AJ17" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="1:35">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A18" s="13">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -20517,18 +20526,19 @@
       <c r="AD18" s="12"/>
       <c r="AE18" s="12"/>
       <c r="AF18" s="12"/>
-      <c r="AG18" s="12" t="str">
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH18" s="37" t="s">
+      <c r="AI18" s="37" t="s">
         <v>243</v>
       </c>
-      <c r="AI18" s="42" t="s">
+      <c r="AJ18" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="19" spans="1:35">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A19" s="13">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -20618,18 +20628,19 @@
       <c r="AD19" s="12"/>
       <c r="AE19" s="12"/>
       <c r="AF19" s="12"/>
-      <c r="AG19" s="12" t="str">
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2004, 2015, </v>
       </c>
-      <c r="AH19" s="37" t="s">
+      <c r="AI19" s="37" t="s">
         <v>244</v>
       </c>
-      <c r="AI19" s="42" t="s">
+      <c r="AJ19" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="20" spans="1:35">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="13">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -20719,18 +20730,19 @@
       <c r="AD20" s="12"/>
       <c r="AE20" s="12"/>
       <c r="AF20" s="12"/>
-      <c r="AG20" s="12" t="str">
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 2006, 2017, </v>
       </c>
-      <c r="AH20" s="37" t="s">
+      <c r="AI20" s="37" t="s">
         <v>245</v>
       </c>
-      <c r="AI20" s="42" t="s">
+      <c r="AJ20" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="21" spans="1:35">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="13">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -20820,18 +20832,19 @@
       <c r="AD21" s="12"/>
       <c r="AE21" s="12"/>
       <c r="AF21" s="12"/>
-      <c r="AG21" s="12" t="str">
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2010, 2020, </v>
       </c>
-      <c r="AH21" s="37" t="s">
+      <c r="AI21" s="37" t="s">
         <v>246</v>
       </c>
-      <c r="AI21" s="42" t="s">
+      <c r="AJ21" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="22" spans="1:35">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A22" s="13">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -20921,18 +20934,19 @@
       <c r="AD22" s="12"/>
       <c r="AE22" s="12"/>
       <c r="AF22" s="12"/>
-      <c r="AG22" s="12" t="str">
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2010, </v>
       </c>
-      <c r="AH22" s="37" t="s">
+      <c r="AI22" s="37" t="s">
         <v>247</v>
       </c>
-      <c r="AI22" s="42" t="s">
+      <c r="AJ22" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:35">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A23" s="13">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -21022,18 +21036,19 @@
       <c r="AD23" s="12"/>
       <c r="AE23" s="12"/>
       <c r="AF23" s="12"/>
-      <c r="AG23" s="12" t="str">
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH23" s="37" t="s">
+      <c r="AI23" s="37" t="s">
         <v>248</v>
       </c>
-      <c r="AI23" s="42" t="s">
+      <c r="AJ23" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="24" spans="1:35">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" s="13">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -21123,18 +21138,19 @@
       <c r="AD24" s="12"/>
       <c r="AE24" s="12"/>
       <c r="AF24" s="12"/>
-      <c r="AG24" s="12" t="str">
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2004, 2015, </v>
       </c>
-      <c r="AH24" s="37" t="s">
+      <c r="AI24" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="AI24" s="42" t="s">
+      <c r="AJ24" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="25" spans="1:35">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="13">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -21224,18 +21240,19 @@
       <c r="AD25" s="12"/>
       <c r="AE25" s="12"/>
       <c r="AF25" s="12"/>
-      <c r="AG25" s="12" t="str">
+      <c r="AG25" s="12"/>
+      <c r="AH25" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2013, </v>
       </c>
-      <c r="AH25" s="37" t="s">
+      <c r="AI25" s="37" t="s">
         <v>250</v>
       </c>
-      <c r="AI25" s="42" t="s">
+      <c r="AJ25" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="1:35">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="13">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -21325,18 +21342,19 @@
       <c r="AD26" s="12"/>
       <c r="AE26" s="12"/>
       <c r="AF26" s="12"/>
-      <c r="AG26" s="12" t="str">
+      <c r="AG26" s="12"/>
+      <c r="AH26" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH26" s="37" t="s">
+      <c r="AI26" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="AI26" s="42" t="s">
+      <c r="AJ26" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="1:35">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" s="13">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -21426,18 +21444,19 @@
       <c r="AD27" s="12"/>
       <c r="AE27" s="12"/>
       <c r="AF27" s="12"/>
-      <c r="AG27" s="12" t="str">
+      <c r="AG27" s="12"/>
+      <c r="AH27" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH27" s="37" t="s">
+      <c r="AI27" s="37" t="s">
         <v>252</v>
       </c>
-      <c r="AI27" s="42" t="s">
+      <c r="AJ27" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="28" spans="1:35">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A28" s="13">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -21527,18 +21546,19 @@
       <c r="AD28" s="12"/>
       <c r="AE28" s="12"/>
       <c r="AF28" s="12"/>
-      <c r="AG28" s="12" t="str">
+      <c r="AG28" s="12"/>
+      <c r="AH28" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH28" s="37" t="s">
+      <c r="AI28" s="37" t="s">
         <v>253</v>
       </c>
-      <c r="AI28" s="42" t="s">
+      <c r="AJ28" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="29" spans="1:35">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" s="13">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -21630,18 +21650,19 @@
       <c r="AD29" s="12"/>
       <c r="AE29" s="12"/>
       <c r="AF29" s="12"/>
-      <c r="AG29" s="12" t="str">
+      <c r="AG29" s="12"/>
+      <c r="AH29" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1997, 2007, 2021, </v>
       </c>
-      <c r="AH29" s="37" t="s">
+      <c r="AI29" s="37" t="s">
         <v>254</v>
       </c>
-      <c r="AI29" s="42" t="s">
+      <c r="AJ29" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="30" spans="1:35">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="13">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -21731,18 +21752,19 @@
       <c r="AD30" s="12"/>
       <c r="AE30" s="12"/>
       <c r="AF30" s="12"/>
-      <c r="AG30" s="12" t="str">
+      <c r="AG30" s="12"/>
+      <c r="AH30" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1997, 2007, 2016, </v>
       </c>
-      <c r="AH30" s="37" t="s">
+      <c r="AI30" s="37" t="s">
         <v>255</v>
       </c>
-      <c r="AI30" s="42" t="s">
+      <c r="AJ30" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="31" spans="1:35">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="13">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -21832,18 +21854,19 @@
       <c r="AD31" s="12"/>
       <c r="AE31" s="12"/>
       <c r="AF31" s="12"/>
-      <c r="AG31" s="12" t="str">
+      <c r="AG31" s="12"/>
+      <c r="AH31" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2001, 2014, </v>
       </c>
-      <c r="AH31" s="37" t="s">
+      <c r="AI31" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="AI31" s="42" t="s">
+      <c r="AJ31" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="32" spans="1:35">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="13">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -21933,18 +21956,19 @@
       <c r="AD32" s="12"/>
       <c r="AE32" s="12"/>
       <c r="AF32" s="12"/>
-      <c r="AG32" s="12" t="str">
+      <c r="AG32" s="12"/>
+      <c r="AH32" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2004, </v>
       </c>
-      <c r="AH32" s="37" t="s">
+      <c r="AI32" s="37" t="s">
         <v>257</v>
       </c>
-      <c r="AI32" s="42" t="s">
+      <c r="AJ32" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="33" spans="1:36">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A33" s="13">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -22034,18 +22058,19 @@
       <c r="AD33" s="12"/>
       <c r="AE33" s="12"/>
       <c r="AF33" s="12"/>
-      <c r="AG33" s="12" t="str">
+      <c r="AG33" s="12"/>
+      <c r="AH33" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH33" s="37" t="s">
+      <c r="AI33" s="37" t="s">
         <v>258</v>
       </c>
-      <c r="AI33" s="42" t="s">
+      <c r="AJ33" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="34" spans="1:36">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A34" s="13">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -22135,18 +22160,19 @@
       <c r="AD34" s="12"/>
       <c r="AE34" s="12"/>
       <c r="AF34" s="12"/>
-      <c r="AG34" s="12" t="str">
+      <c r="AG34" s="12"/>
+      <c r="AH34" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2015, </v>
       </c>
-      <c r="AH34" s="37" t="s">
+      <c r="AI34" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="AI34" s="42" t="s">
+      <c r="AJ34" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="35" spans="1:36">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A35" s="13">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -22236,18 +22262,19 @@
       <c r="AD35" s="12"/>
       <c r="AE35" s="12"/>
       <c r="AF35" s="12"/>
-      <c r="AG35" s="12" t="str">
+      <c r="AG35" s="12"/>
+      <c r="AH35" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2014, </v>
       </c>
-      <c r="AH35" s="37" t="s">
+      <c r="AI35" s="37" t="s">
         <v>260</v>
       </c>
-      <c r="AI35" s="42" t="s">
+      <c r="AJ35" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="36" spans="1:36">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A36" s="13">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -22337,18 +22364,19 @@
       <c r="AD36" s="12"/>
       <c r="AE36" s="12"/>
       <c r="AF36" s="12"/>
-      <c r="AG36" s="12" t="str">
+      <c r="AG36" s="12"/>
+      <c r="AH36" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2001, 2015, </v>
       </c>
-      <c r="AH36" s="37" t="s">
+      <c r="AI36" s="37" t="s">
         <v>261</v>
       </c>
-      <c r="AI36" s="42" t="s">
+      <c r="AJ36" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="37" spans="1:36">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A37" s="13">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -22438,18 +22466,19 @@
       <c r="AD37" s="12"/>
       <c r="AE37" s="12"/>
       <c r="AF37" s="12"/>
-      <c r="AG37" s="12" t="str">
+      <c r="AG37" s="12"/>
+      <c r="AH37" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2010, 2020, </v>
       </c>
-      <c r="AH37" s="37" t="s">
+      <c r="AI37" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="AI37" s="42" t="s">
+      <c r="AJ37" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="38" spans="1:36">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A38" s="13">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -22539,18 +22568,19 @@
       <c r="AD38" s="12"/>
       <c r="AE38" s="12"/>
       <c r="AF38" s="12"/>
-      <c r="AG38" s="12" t="str">
+      <c r="AG38" s="12"/>
+      <c r="AH38" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH38" s="37" t="s">
+      <c r="AI38" s="37" t="s">
         <v>263</v>
       </c>
-      <c r="AI38" s="42" t="s">
+      <c r="AJ38" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="39" spans="1:36">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A39" s="13">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -22640,18 +22670,19 @@
       <c r="AD39" s="12"/>
       <c r="AE39" s="12"/>
       <c r="AF39" s="12"/>
-      <c r="AG39" s="12" t="str">
+      <c r="AG39" s="12"/>
+      <c r="AH39" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH39" s="37" t="s">
+      <c r="AI39" s="37" t="s">
         <v>264</v>
       </c>
-      <c r="AI39" s="42" t="s">
+      <c r="AJ39" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="40" spans="1:36">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A40" s="13">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -22741,21 +22772,22 @@
       <c r="AD40" s="12"/>
       <c r="AE40" s="12"/>
       <c r="AF40" s="12"/>
-      <c r="AG40" s="12" t="str">
+      <c r="AG40" s="12"/>
+      <c r="AH40" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2015, </v>
       </c>
-      <c r="AH40" s="37" t="s">
+      <c r="AI40" s="37" t="s">
         <v>265</v>
       </c>
-      <c r="AI40" s="42" t="s">
+      <c r="AJ40" s="42" t="s">
         <v>229</v>
       </c>
-      <c r="AJ40" s="41" t="s">
+      <c r="AK40" s="41" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="41" spans="1:36">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A41" s="13">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -22845,18 +22877,19 @@
       <c r="AD41" s="12"/>
       <c r="AE41" s="12"/>
       <c r="AF41" s="12"/>
-      <c r="AG41" s="12" t="str">
+      <c r="AG41" s="12"/>
+      <c r="AH41" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2000, </v>
       </c>
-      <c r="AH41" s="37" t="s">
+      <c r="AI41" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="AI41" s="42" t="s">
+      <c r="AJ41" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="42" spans="1:36">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A42" s="13">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -22946,18 +22979,19 @@
       <c r="AD42" s="12"/>
       <c r="AE42" s="12"/>
       <c r="AF42" s="12"/>
-      <c r="AG42" s="12" t="str">
+      <c r="AG42" s="12"/>
+      <c r="AH42" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2000, 2010, </v>
       </c>
-      <c r="AH42" s="37" t="s">
+      <c r="AI42" s="37" t="s">
         <v>268</v>
       </c>
-      <c r="AI42" s="42" t="s">
+      <c r="AJ42" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="43" spans="1:36">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A43" s="13">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -23047,18 +23081,19 @@
       <c r="AD43" s="12"/>
       <c r="AE43" s="12"/>
       <c r="AF43" s="12"/>
-      <c r="AG43" s="12" t="str">
+      <c r="AG43" s="12"/>
+      <c r="AH43" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2008, </v>
       </c>
-      <c r="AH43" s="37" t="s">
+      <c r="AI43" s="37" t="s">
         <v>269</v>
       </c>
-      <c r="AI43" s="42" t="s">
+      <c r="AJ43" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="44" spans="1:36">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A44" s="13">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -23148,18 +23183,19 @@
       <c r="AD44" s="12"/>
       <c r="AE44" s="12"/>
       <c r="AF44" s="12"/>
-      <c r="AG44" s="12" t="str">
+      <c r="AG44" s="12"/>
+      <c r="AH44" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2015, </v>
       </c>
-      <c r="AH44" s="37" t="s">
+      <c r="AI44" s="37" t="s">
         <v>270</v>
       </c>
-      <c r="AI44" s="42" t="s">
+      <c r="AJ44" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="45" spans="1:36">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A45" s="13">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -23249,18 +23285,19 @@
       <c r="AD45" s="12"/>
       <c r="AE45" s="12"/>
       <c r="AF45" s="12"/>
-      <c r="AG45" s="12" t="str">
+      <c r="AG45" s="12"/>
+      <c r="AH45" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH45" s="37" t="s">
+      <c r="AI45" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="AI45" s="42" t="s">
+      <c r="AJ45" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="46" spans="1:36">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A46" s="13">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -23350,18 +23387,19 @@
       <c r="AD46" s="12"/>
       <c r="AE46" s="12"/>
       <c r="AF46" s="12"/>
-      <c r="AG46" s="12" t="str">
+      <c r="AG46" s="12"/>
+      <c r="AH46" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2013, </v>
       </c>
-      <c r="AH46" s="37" t="s">
+      <c r="AI46" s="37" t="s">
         <v>272</v>
       </c>
-      <c r="AI46" s="42" t="s">
+      <c r="AJ46" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="47" spans="1:36">
+    <row r="47" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A47" s="13">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -23451,18 +23489,19 @@
       <c r="AD47" s="12"/>
       <c r="AE47" s="12"/>
       <c r="AF47" s="12"/>
-      <c r="AG47" s="12" t="str">
+      <c r="AG47" s="12"/>
+      <c r="AH47" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2002, </v>
       </c>
-      <c r="AH47" s="37" t="s">
+      <c r="AI47" s="37" t="s">
         <v>273</v>
       </c>
-      <c r="AI47" s="42" t="s">
+      <c r="AJ47" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="48" spans="1:36">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A48" s="13">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -23552,18 +23591,19 @@
       <c r="AD48" s="12"/>
       <c r="AE48" s="12"/>
       <c r="AF48" s="12"/>
-      <c r="AG48" s="12" t="str">
+      <c r="AG48" s="12"/>
+      <c r="AH48" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2009, 2020, </v>
       </c>
-      <c r="AH48" s="37" t="s">
+      <c r="AI48" s="37" t="s">
         <v>274</v>
       </c>
-      <c r="AI48" s="42" t="s">
+      <c r="AJ48" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="49" spans="1:35">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A49" s="13">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -23653,18 +23693,19 @@
       <c r="AD49" s="12"/>
       <c r="AE49" s="12"/>
       <c r="AF49" s="12"/>
-      <c r="AG49" s="12" t="str">
+      <c r="AG49" s="12"/>
+      <c r="AH49" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2020, </v>
       </c>
-      <c r="AH49" s="37" t="s">
+      <c r="AI49" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="AI49" s="42" t="s">
+      <c r="AJ49" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="50" spans="1:35">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A50" s="13">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -23754,18 +23795,19 @@
       <c r="AD50" s="12"/>
       <c r="AE50" s="12"/>
       <c r="AF50" s="12"/>
-      <c r="AG50" s="12" t="str">
+      <c r="AG50" s="12"/>
+      <c r="AH50" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2002, 2012, </v>
       </c>
-      <c r="AH50" s="37" t="s">
+      <c r="AI50" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="AI50" s="42" t="s">
+      <c r="AJ50" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="51" spans="1:35">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A51" s="13">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -23855,18 +23897,19 @@
       <c r="AD51" s="12"/>
       <c r="AE51" s="12"/>
       <c r="AF51" s="12"/>
-      <c r="AG51" s="12" t="str">
+      <c r="AG51" s="12"/>
+      <c r="AH51" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2004, 2014, </v>
       </c>
-      <c r="AH51" s="37" t="s">
+      <c r="AI51" s="37" t="s">
         <v>277</v>
       </c>
-      <c r="AI51" s="42" t="s">
+      <c r="AJ51" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="52" spans="1:35">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A52" s="13">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -23956,18 +23999,19 @@
       <c r="AD52" s="12"/>
       <c r="AE52" s="12"/>
       <c r="AF52" s="12"/>
-      <c r="AG52" s="12" t="str">
+      <c r="AG52" s="12"/>
+      <c r="AH52" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2018, </v>
       </c>
-      <c r="AH52" s="37" t="s">
+      <c r="AI52" s="37" t="s">
         <v>278</v>
       </c>
-      <c r="AI52" s="42" t="s">
+      <c r="AJ52" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="53" spans="1:35">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A53" s="13">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -24057,18 +24101,19 @@
       <c r="AD53" s="12"/>
       <c r="AE53" s="12"/>
       <c r="AF53" s="12"/>
-      <c r="AG53" s="12" t="str">
+      <c r="AG53" s="12"/>
+      <c r="AH53" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2012, </v>
       </c>
-      <c r="AH53" s="37" t="s">
+      <c r="AI53" s="37" t="s">
         <v>279</v>
       </c>
-      <c r="AI53" s="42" t="s">
+      <c r="AJ53" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="54" spans="1:35">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A54" s="13">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -24158,18 +24203,19 @@
       <c r="AD54" s="12"/>
       <c r="AE54" s="12"/>
       <c r="AF54" s="12"/>
-      <c r="AG54" s="12" t="str">
+      <c r="AG54" s="12"/>
+      <c r="AH54" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, </v>
       </c>
-      <c r="AH54" s="37" t="s">
+      <c r="AI54" s="37" t="s">
         <v>280</v>
       </c>
-      <c r="AI54" s="42" t="s">
+      <c r="AJ54" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="55" spans="1:35">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A55" s="13">
         <f t="shared" si="1"/>
         <v>52</v>
@@ -24259,18 +24305,19 @@
       <c r="AD55" s="12"/>
       <c r="AE55" s="12"/>
       <c r="AF55" s="12"/>
-      <c r="AG55" s="12" t="str">
+      <c r="AG55" s="12"/>
+      <c r="AH55" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2001, </v>
       </c>
-      <c r="AH55" s="37" t="s">
+      <c r="AI55" s="37" t="s">
         <v>281</v>
       </c>
-      <c r="AI55" s="42" t="s">
+      <c r="AJ55" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="56" spans="1:35">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A56" s="13">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -24360,18 +24407,19 @@
       <c r="AD56" s="12"/>
       <c r="AE56" s="12"/>
       <c r="AF56" s="12"/>
-      <c r="AG56" s="12" t="str">
+      <c r="AG56" s="12"/>
+      <c r="AH56" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH56" s="37" t="s">
+      <c r="AI56" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="AI56" s="42" t="s">
+      <c r="AJ56" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="57" spans="1:35">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A57" s="13">
         <f t="shared" si="1"/>
         <v>54</v>
@@ -24461,18 +24509,19 @@
       <c r="AD57" s="12"/>
       <c r="AE57" s="12"/>
       <c r="AF57" s="12"/>
-      <c r="AG57" s="12" t="str">
+      <c r="AG57" s="12"/>
+      <c r="AH57" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH57" s="37" t="s">
+      <c r="AI57" s="37" t="s">
         <v>283</v>
       </c>
-      <c r="AI57" s="42" t="s">
+      <c r="AJ57" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="58" spans="1:35">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A58" s="13">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -24562,18 +24611,19 @@
       <c r="AD58" s="12"/>
       <c r="AE58" s="12"/>
       <c r="AF58" s="12"/>
-      <c r="AG58" s="12" t="str">
+      <c r="AG58" s="12"/>
+      <c r="AH58" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2009, </v>
       </c>
-      <c r="AH58" s="37" t="s">
+      <c r="AI58" s="37" t="s">
         <v>284</v>
       </c>
-      <c r="AI58" s="42" t="s">
+      <c r="AJ58" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="59" spans="1:35">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A59" s="13">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -24663,18 +24713,19 @@
       <c r="AD59" s="12"/>
       <c r="AE59" s="12"/>
       <c r="AF59" s="12"/>
-      <c r="AG59" s="12" t="str">
+      <c r="AG59" s="12"/>
+      <c r="AH59" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH59" s="37" t="s">
+      <c r="AI59" s="37" t="s">
         <v>285</v>
       </c>
-      <c r="AI59" s="42" t="s">
+      <c r="AJ59" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="60" spans="1:35">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A60" s="13">
         <f t="shared" si="1"/>
         <v>57</v>
@@ -24764,18 +24815,19 @@
       <c r="AD60" s="12"/>
       <c r="AE60" s="12"/>
       <c r="AF60" s="12"/>
-      <c r="AG60" s="12" t="str">
+      <c r="AG60" s="12"/>
+      <c r="AH60" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 2001, 2011, 2016, </v>
       </c>
-      <c r="AH60" s="37" t="s">
+      <c r="AI60" s="37" t="s">
         <v>286</v>
       </c>
-      <c r="AI60" s="42" t="s">
+      <c r="AJ60" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="61" spans="1:35">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A61" s="13">
         <f t="shared" si="1"/>
         <v>58</v>
@@ -24867,18 +24919,19 @@
         <v>1</v>
       </c>
       <c r="AF61" s="12"/>
-      <c r="AG61" s="12" t="str">
+      <c r="AG61" s="12"/>
+      <c r="AH61" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2013, 2023, </v>
       </c>
-      <c r="AH61" s="37" t="s">
+      <c r="AI61" s="37" t="s">
         <v>287</v>
       </c>
-      <c r="AI61" s="42" t="s">
+      <c r="AJ61" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="62" spans="1:35">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A62" s="13">
         <f t="shared" si="1"/>
         <v>59</v>
@@ -24968,18 +25021,19 @@
       <c r="AD62" s="12"/>
       <c r="AE62" s="12"/>
       <c r="AF62" s="12"/>
-      <c r="AG62" s="12" t="str">
+      <c r="AG62" s="12"/>
+      <c r="AH62" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2014, </v>
       </c>
-      <c r="AH62" s="37" t="s">
+      <c r="AI62" s="37" t="s">
         <v>288</v>
       </c>
-      <c r="AI62" s="42" t="s">
+      <c r="AJ62" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="63" spans="1:35">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A63" s="13">
         <f t="shared" si="1"/>
         <v>60</v>
@@ -25069,18 +25123,19 @@
       <c r="AD63" s="12"/>
       <c r="AE63" s="12"/>
       <c r="AF63" s="12"/>
-      <c r="AG63" s="12" t="str">
+      <c r="AG63" s="12"/>
+      <c r="AH63" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AH63" s="37" t="s">
+      <c r="AI63" s="37" t="s">
         <v>289</v>
       </c>
-      <c r="AI63" s="42" t="s">
+      <c r="AJ63" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="1:35">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A64" s="13">
         <f t="shared" si="1"/>
         <v>61</v>
@@ -25170,18 +25225,19 @@
       <c r="AD64" s="12"/>
       <c r="AE64" s="12"/>
       <c r="AF64" s="12"/>
-      <c r="AG64" s="12" t="str">
+      <c r="AG64" s="12"/>
+      <c r="AH64" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 2007, </v>
       </c>
-      <c r="AH64" s="37" t="s">
+      <c r="AI64" s="37" t="s">
         <v>290</v>
       </c>
-      <c r="AI64" s="42" t="s">
+      <c r="AJ64" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="65" spans="1:35">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A65" s="13">
         <f t="shared" si="1"/>
         <v>62</v>
@@ -25271,18 +25327,19 @@
       <c r="AD65" s="12"/>
       <c r="AE65" s="12"/>
       <c r="AF65" s="12"/>
-      <c r="AG65" s="12" t="str">
+      <c r="AG65" s="12"/>
+      <c r="AH65" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1997, 2007, 2017, </v>
       </c>
-      <c r="AH65" s="37" t="s">
+      <c r="AI65" s="37" t="s">
         <v>291</v>
       </c>
-      <c r="AI65" s="42" t="s">
+      <c r="AJ65" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="66" spans="1:35">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A66" s="13">
         <f t="shared" si="1"/>
         <v>63</v>
@@ -25372,18 +25429,19 @@
       <c r="AD66" s="12"/>
       <c r="AE66" s="12"/>
       <c r="AF66" s="12"/>
-      <c r="AG66" s="12" t="str">
+      <c r="AG66" s="12"/>
+      <c r="AH66" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2006, </v>
       </c>
-      <c r="AH66" s="37" t="s">
+      <c r="AI66" s="37" t="s">
         <v>292</v>
       </c>
-      <c r="AI66" s="42" t="s">
+      <c r="AJ66" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="67" spans="1:35">
+    <row r="67" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A67" s="13">
         <f t="shared" si="1"/>
         <v>64</v>
@@ -25473,18 +25531,19 @@
       <c r="AD67" s="12"/>
       <c r="AE67" s="12"/>
       <c r="AF67" s="12"/>
-      <c r="AG67" s="12" t="str">
+      <c r="AG67" s="12"/>
+      <c r="AH67" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2019, </v>
       </c>
-      <c r="AH67" s="37" t="s">
+      <c r="AI67" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="AI67" s="42" t="s">
+      <c r="AJ67" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="68" spans="1:35">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A68" s="13">
         <f t="shared" si="1"/>
         <v>65</v>
@@ -25574,20 +25633,21 @@
       <c r="AD68" s="12"/>
       <c r="AE68" s="12"/>
       <c r="AF68" s="12"/>
-      <c r="AG68" s="12" t="str">
-        <f t="shared" ref="AG68:AG131" si="3">+IF($D68=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E68=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F68=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G68=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H68=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I68=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J68=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K68=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L68=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M68=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N68=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O68=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P68=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q68=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R68=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S68=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T68=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U68=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V68=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W68=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X68=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y68=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z68=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA68=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB68=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC68=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD68=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE68=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF68=1, RIGHT(AF$3,4)&amp;", ", "")</f>
+      <c r="AG68" s="12"/>
+      <c r="AH68" s="12" t="str">
+        <f t="shared" si="2"/>
         <v xml:space="preserve">2020, </v>
       </c>
-      <c r="AH68" s="37" t="s">
+      <c r="AI68" s="37" t="s">
         <v>294</v>
       </c>
-      <c r="AI68" s="42" t="s">
+      <c r="AJ68" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="69" spans="1:35">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A69" s="13">
-        <f t="shared" ref="A69:A132" si="4">1+A68</f>
+        <f t="shared" ref="A69:A132" si="3">1+A68</f>
         <v>66</v>
       </c>
       <c r="B69" s="14" t="s">
@@ -25675,20 +25735,21 @@
       <c r="AD69" s="12"/>
       <c r="AE69" s="12"/>
       <c r="AF69" s="12"/>
-      <c r="AG69" s="12" t="str">
+      <c r="AG69" s="12"/>
+      <c r="AH69" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">2014, 2020, </v>
+      </c>
+      <c r="AI69" s="37" t="s">
+        <v>295</v>
+      </c>
+      <c r="AJ69" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="70" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A70" s="13">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2014, 2020, </v>
-      </c>
-      <c r="AH69" s="37" t="s">
-        <v>295</v>
-      </c>
-      <c r="AI69" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="70" spans="1:35">
-      <c r="A70" s="13">
-        <f t="shared" si="4"/>
         <v>67</v>
       </c>
       <c r="B70" s="14" t="s">
@@ -25776,20 +25837,21 @@
       <c r="AD70" s="12"/>
       <c r="AE70" s="12"/>
       <c r="AF70" s="12"/>
-      <c r="AG70" s="12" t="str">
+      <c r="AG70" s="12"/>
+      <c r="AH70" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">2002, </v>
+      </c>
+      <c r="AI70" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="AJ70" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="71" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A71" s="13">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2002, </v>
-      </c>
-      <c r="AH70" s="37" t="s">
-        <v>296</v>
-      </c>
-      <c r="AI70" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="71" spans="1:35">
-      <c r="A71" s="13">
-        <f t="shared" si="4"/>
         <v>68</v>
       </c>
       <c r="B71" s="19" t="s">
@@ -25875,20 +25937,21 @@
       <c r="AD71" s="12"/>
       <c r="AE71" s="12"/>
       <c r="AF71" s="12"/>
-      <c r="AG71" s="12" t="str">
+      <c r="AG71" s="12"/>
+      <c r="AH71" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">1999, 2011, 2020, </v>
+      </c>
+      <c r="AI71" s="37" t="s">
+        <v>297</v>
+      </c>
+      <c r="AJ71" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="72" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A72" s="13">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">1999, 2011, 2020, </v>
-      </c>
-      <c r="AH71" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="AI71" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="72" spans="1:35">
-      <c r="A72" s="13">
-        <f t="shared" si="4"/>
         <v>69</v>
       </c>
       <c r="B72" s="15" t="s">
@@ -25978,20 +26041,21 @@
         <v>299</v>
       </c>
       <c r="AF72" s="12"/>
-      <c r="AG72" s="12" t="str">
+      <c r="AG72" s="12"/>
+      <c r="AH72" s="12" t="str">
+        <f t="shared" ref="AH72:AH135" si="4">+IF($D72=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E72=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F72=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G72=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H72=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I72=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J72=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K72=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L72=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M72=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N72=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O72=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P72=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q72=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R72=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S72=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T72=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U72=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V72=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W72=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X72=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y72=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z72=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA72=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB72=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC72=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD72=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE72=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF72=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG72=1, RIGHT(AG$3,4)&amp;", ", "")</f>
+        <v xml:space="preserve">1999, 2010, </v>
+      </c>
+      <c r="AI72" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="AJ72" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="73" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A73" s="13">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">1999, 2010, </v>
-      </c>
-      <c r="AH72" s="37" t="s">
-        <v>298</v>
-      </c>
-      <c r="AI72" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="73" spans="1:35">
-      <c r="A73" s="13">
-        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="B73" s="14" t="s">
@@ -26079,20 +26143,21 @@
       <c r="AD73" s="12"/>
       <c r="AE73" s="12"/>
       <c r="AF73" s="12"/>
-      <c r="AG73" s="12" t="str">
+      <c r="AG73" s="12"/>
+      <c r="AH73" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">1999, 2009, 2020, </v>
+      </c>
+      <c r="AI73" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="AJ73" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="74" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A74" s="13">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">1999, 2009, 2020, </v>
-      </c>
-      <c r="AH73" s="37" t="s">
-        <v>300</v>
-      </c>
-      <c r="AI73" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="74" spans="1:35">
-      <c r="A74" s="13">
-        <f t="shared" si="4"/>
         <v>71</v>
       </c>
       <c r="B74" s="14" t="s">
@@ -26180,20 +26245,21 @@
       <c r="AD74" s="12"/>
       <c r="AE74" s="12"/>
       <c r="AF74" s="12"/>
-      <c r="AG74" s="12" t="str">
+      <c r="AG74" s="12"/>
+      <c r="AH74" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI74" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="AJ74" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="75" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A75" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AH74" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="AI74" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="75" spans="1:35">
-      <c r="A75" s="13">
-        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="B75" s="14" t="s">
@@ -26281,20 +26347,21 @@
       <c r="AD75" s="12"/>
       <c r="AE75" s="12"/>
       <c r="AF75" s="12"/>
-      <c r="AG75" s="12" t="str">
+      <c r="AG75" s="12"/>
+      <c r="AH75" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2001, </v>
+      </c>
+      <c r="AI75" s="37" t="s">
+        <v>302</v>
+      </c>
+      <c r="AJ75" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="76" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A76" s="13">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2001, </v>
-      </c>
-      <c r="AH75" s="37" t="s">
-        <v>302</v>
-      </c>
-      <c r="AI75" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="76" spans="1:35">
-      <c r="A76" s="13">
-        <f t="shared" si="4"/>
         <v>73</v>
       </c>
       <c r="B76" s="15" t="s">
@@ -26382,20 +26449,21 @@
       <c r="AD76" s="12"/>
       <c r="AE76" s="12"/>
       <c r="AF76" s="12"/>
-      <c r="AG76" s="12" t="str">
+      <c r="AG76" s="12"/>
+      <c r="AH76" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2007, 2020, </v>
+      </c>
+      <c r="AI76" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="AJ76" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="77" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2007, 2020, </v>
-      </c>
-      <c r="AH76" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="AI76" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="77" spans="1:35" s="3" customFormat="1">
-      <c r="A77" s="20">
-        <f t="shared" si="4"/>
         <v>74</v>
       </c>
       <c r="B77" s="21" t="s">
@@ -26483,20 +26551,21 @@
       <c r="AD77" s="27"/>
       <c r="AE77" s="27"/>
       <c r="AF77" s="27"/>
-      <c r="AG77" s="12" t="str">
+      <c r="AG77" s="27"/>
+      <c r="AH77" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2004, </v>
+      </c>
+      <c r="AI77" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="AJ77" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="78" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2004, </v>
-      </c>
-      <c r="AH77" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="AI77" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="78" spans="1:35" s="3" customFormat="1">
-      <c r="A78" s="20">
-        <f t="shared" si="4"/>
         <v>75</v>
       </c>
       <c r="B78" s="22" t="s">
@@ -26584,20 +26653,21 @@
       <c r="AD78" s="27"/>
       <c r="AE78" s="27"/>
       <c r="AF78" s="27"/>
-      <c r="AG78" s="12" t="str">
+      <c r="AG78" s="27"/>
+      <c r="AH78" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2006, </v>
+      </c>
+      <c r="AI78" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="AJ78" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="79" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2006, </v>
-      </c>
-      <c r="AH78" s="37" t="s">
-        <v>305</v>
-      </c>
-      <c r="AI78" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="79" spans="1:35" s="3" customFormat="1">
-      <c r="A79" s="20">
-        <f t="shared" si="4"/>
         <v>76</v>
       </c>
       <c r="B79" s="21" t="s">
@@ -26685,20 +26755,21 @@
       <c r="AD79" s="27"/>
       <c r="AE79" s="27"/>
       <c r="AF79" s="27"/>
-      <c r="AG79" s="12" t="str">
+      <c r="AG79" s="27"/>
+      <c r="AH79" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2005, </v>
+      </c>
+      <c r="AI79" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="AJ79" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="80" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2005, </v>
-      </c>
-      <c r="AH79" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="AI79" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="80" spans="1:35" s="3" customFormat="1">
-      <c r="A80" s="20">
-        <f t="shared" si="4"/>
         <v>77</v>
       </c>
       <c r="B80" s="21" t="s">
@@ -26786,20 +26857,21 @@
       <c r="AD80" s="27"/>
       <c r="AE80" s="27"/>
       <c r="AF80" s="27"/>
-      <c r="AG80" s="12" t="str">
+      <c r="AG80" s="27"/>
+      <c r="AH80" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI80" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="AJ80" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="81" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="20">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AH80" s="37" t="s">
-        <v>307</v>
-      </c>
-      <c r="AI80" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="81" spans="1:35" s="3" customFormat="1">
-      <c r="A81" s="20">
-        <f t="shared" si="4"/>
         <v>78</v>
       </c>
       <c r="B81" s="21" t="s">
@@ -26887,20 +26959,21 @@
       <c r="AD81" s="27"/>
       <c r="AE81" s="27"/>
       <c r="AF81" s="27"/>
-      <c r="AG81" s="12" t="str">
+      <c r="AG81" s="27"/>
+      <c r="AH81" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2005, </v>
+      </c>
+      <c r="AI81" s="37" t="s">
+        <v>308</v>
+      </c>
+      <c r="AJ81" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="82" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2005, </v>
-      </c>
-      <c r="AH81" s="37" t="s">
-        <v>308</v>
-      </c>
-      <c r="AI81" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="82" spans="1:35" s="3" customFormat="1">
-      <c r="A82" s="20">
-        <f t="shared" si="4"/>
         <v>79</v>
       </c>
       <c r="B82" s="22" t="s">
@@ -26990,20 +27063,21 @@
       <c r="AD82" s="27"/>
       <c r="AE82" s="27"/>
       <c r="AF82" s="27"/>
-      <c r="AG82" s="12" t="str">
+      <c r="AG82" s="27"/>
+      <c r="AH82" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2021, </v>
+      </c>
+      <c r="AI82" s="37" t="s">
+        <v>309</v>
+      </c>
+      <c r="AJ82" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="83" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2021, </v>
-      </c>
-      <c r="AH82" s="37" t="s">
-        <v>309</v>
-      </c>
-      <c r="AI82" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="83" spans="1:35" s="3" customFormat="1">
-      <c r="A83" s="20">
-        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="B83" s="23" t="s">
@@ -27091,20 +27165,21 @@
       <c r="AD83" s="27"/>
       <c r="AE83" s="27"/>
       <c r="AF83" s="27"/>
-      <c r="AG83" s="12" t="str">
+      <c r="AG83" s="27"/>
+      <c r="AH83" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI83" s="37" t="s">
+        <v>310</v>
+      </c>
+      <c r="AJ83" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="84" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="20">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AH83" s="37" t="s">
-        <v>310</v>
-      </c>
-      <c r="AI83" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="84" spans="1:35" s="3" customFormat="1">
-      <c r="A84" s="20">
-        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="B84" s="21" t="s">
@@ -27192,20 +27267,21 @@
       <c r="AD84" s="27"/>
       <c r="AE84" s="27"/>
       <c r="AF84" s="27"/>
-      <c r="AG84" s="12" t="str">
+      <c r="AG84" s="27"/>
+      <c r="AH84" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2014, </v>
+      </c>
+      <c r="AI84" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="AJ84" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="85" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2014, </v>
-      </c>
-      <c r="AH84" s="37" t="s">
-        <v>311</v>
-      </c>
-      <c r="AI84" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="85" spans="1:35" s="3" customFormat="1">
-      <c r="A85" s="20">
-        <f t="shared" si="4"/>
         <v>82</v>
       </c>
       <c r="B85" s="21" t="s">
@@ -27295,20 +27371,21 @@
       </c>
       <c r="AE85" s="27"/>
       <c r="AF85" s="27"/>
-      <c r="AG85" s="12" t="str">
+      <c r="AG85" s="27"/>
+      <c r="AH85" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2007, 2022, </v>
+      </c>
+      <c r="AI85" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="AJ85" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2007, 2022, </v>
-      </c>
-      <c r="AH85" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="AI85" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="86" spans="1:35" s="3" customFormat="1">
-      <c r="A86" s="20">
-        <f t="shared" si="4"/>
         <v>83</v>
       </c>
       <c r="B86" s="21" t="s">
@@ -27396,20 +27473,21 @@
       <c r="AD86" s="27"/>
       <c r="AE86" s="27"/>
       <c r="AF86" s="27"/>
-      <c r="AG86" s="12" t="str">
+      <c r="AG86" s="27"/>
+      <c r="AH86" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2016, </v>
+      </c>
+      <c r="AI86" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="AJ86" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="87" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2016, </v>
-      </c>
-      <c r="AH86" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="AI86" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="87" spans="1:35" s="3" customFormat="1">
-      <c r="A87" s="20">
-        <f t="shared" si="4"/>
         <v>84</v>
       </c>
       <c r="B87" s="21" t="s">
@@ -27497,20 +27575,21 @@
       <c r="AD87" s="27"/>
       <c r="AE87" s="27"/>
       <c r="AF87" s="27"/>
-      <c r="AG87" s="12" t="str">
+      <c r="AG87" s="27"/>
+      <c r="AH87" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2011, </v>
+      </c>
+      <c r="AI87" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="AJ87" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="88" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2011, </v>
-      </c>
-      <c r="AH87" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="AI87" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="88" spans="1:35" s="3" customFormat="1">
-      <c r="A88" s="20">
-        <f t="shared" si="4"/>
         <v>85</v>
       </c>
       <c r="B88" s="21" t="s">
@@ -27598,20 +27677,21 @@
       <c r="AD88" s="27"/>
       <c r="AE88" s="27"/>
       <c r="AF88" s="27"/>
-      <c r="AG88" s="12" t="str">
+      <c r="AG88" s="27"/>
+      <c r="AH88" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2000, 2011, </v>
+      </c>
+      <c r="AI88" s="37" t="s">
+        <v>315</v>
+      </c>
+      <c r="AJ88" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="89" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2000, 2011, </v>
-      </c>
-      <c r="AH88" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="AI88" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="89" spans="1:35" s="3" customFormat="1">
-      <c r="A89" s="20">
-        <f t="shared" si="4"/>
         <v>86</v>
       </c>
       <c r="B89" s="21" t="s">
@@ -27699,20 +27779,21 @@
       <c r="AD89" s="27"/>
       <c r="AE89" s="27"/>
       <c r="AF89" s="27"/>
-      <c r="AG89" s="12" t="str">
+      <c r="AG89" s="27"/>
+      <c r="AH89" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2010, </v>
+      </c>
+      <c r="AI89" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="AJ89" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="90" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2010, </v>
-      </c>
-      <c r="AH89" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="AI89" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="90" spans="1:35" s="3" customFormat="1">
-      <c r="A90" s="20">
-        <f t="shared" si="4"/>
         <v>87</v>
       </c>
       <c r="B90" s="23" t="s">
@@ -27800,20 +27881,21 @@
       <c r="AD90" s="27"/>
       <c r="AE90" s="27"/>
       <c r="AF90" s="27"/>
-      <c r="AG90" s="12" t="str">
+      <c r="AG90" s="27"/>
+      <c r="AH90" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">1996, 2016, </v>
+      </c>
+      <c r="AI90" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ90" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="91" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">1996, 2016, </v>
-      </c>
-      <c r="AH90" s="37" t="s">
-        <v>317</v>
-      </c>
-      <c r="AI90" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="91" spans="1:35" s="3" customFormat="1">
-      <c r="A91" s="20">
-        <f t="shared" si="4"/>
         <v>88</v>
       </c>
       <c r="B91" s="21" t="s">
@@ -27901,20 +27983,21 @@
       <c r="AD91" s="27"/>
       <c r="AE91" s="27"/>
       <c r="AF91" s="27"/>
-      <c r="AG91" s="12" t="str">
+      <c r="AG91" s="27"/>
+      <c r="AH91" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2000, 2009, </v>
+      </c>
+      <c r="AI91" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="AJ91" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="92" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2000, 2009, </v>
-      </c>
-      <c r="AH91" s="37" t="s">
-        <v>318</v>
-      </c>
-      <c r="AI91" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="92" spans="1:35" s="3" customFormat="1">
-      <c r="A92" s="20">
-        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="B92" s="21" t="s">
@@ -28002,20 +28085,21 @@
       <c r="AD92" s="27"/>
       <c r="AE92" s="27"/>
       <c r="AF92" s="27"/>
-      <c r="AG92" s="12" t="str">
+      <c r="AG92" s="27"/>
+      <c r="AH92" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2003, 2010, </v>
+      </c>
+      <c r="AI92" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="AJ92" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="93" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2003, 2010, </v>
-      </c>
-      <c r="AH92" s="37" t="s">
-        <v>319</v>
-      </c>
-      <c r="AI92" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="93" spans="1:35" s="3" customFormat="1">
-      <c r="A93" s="20">
-        <f t="shared" si="4"/>
         <v>90</v>
       </c>
       <c r="B93" s="21" t="s">
@@ -28103,20 +28187,21 @@
       <c r="AD93" s="27"/>
       <c r="AE93" s="27"/>
       <c r="AF93" s="27"/>
-      <c r="AG93" s="12" t="str">
+      <c r="AG93" s="27"/>
+      <c r="AH93" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">1997, 2013, </v>
+      </c>
+      <c r="AI93" s="37" t="s">
+        <v>320</v>
+      </c>
+      <c r="AJ93" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="94" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">1997, 2013, </v>
-      </c>
-      <c r="AH93" s="37" t="s">
-        <v>320</v>
-      </c>
-      <c r="AI93" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="94" spans="1:35" s="3" customFormat="1">
-      <c r="A94" s="20">
-        <f t="shared" si="4"/>
         <v>91</v>
       </c>
       <c r="B94" s="21" t="s">
@@ -28206,20 +28291,21 @@
       <c r="AD94" s="27"/>
       <c r="AE94" s="27"/>
       <c r="AF94" s="27"/>
-      <c r="AG94" s="12" t="str">
+      <c r="AG94" s="27"/>
+      <c r="AH94" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2021, </v>
+      </c>
+      <c r="AI94" s="37" t="s">
+        <v>321</v>
+      </c>
+      <c r="AJ94" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="95" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2021, </v>
-      </c>
-      <c r="AH94" s="37" t="s">
-        <v>321</v>
-      </c>
-      <c r="AI94" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="95" spans="1:35" s="3" customFormat="1">
-      <c r="A95" s="20">
-        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="B95" s="21" t="s">
@@ -28309,20 +28395,21 @@
       <c r="AD95" s="27"/>
       <c r="AE95" s="27"/>
       <c r="AF95" s="27"/>
-      <c r="AG95" s="12" t="str">
+      <c r="AG95" s="27"/>
+      <c r="AH95" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2002, 2011, 2021, </v>
+      </c>
+      <c r="AI95" s="37" t="s">
+        <v>322</v>
+      </c>
+      <c r="AJ95" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="96" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2002, 2011, 2021, </v>
-      </c>
-      <c r="AH95" s="37" t="s">
-        <v>322</v>
-      </c>
-      <c r="AI95" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="96" spans="1:35" s="3" customFormat="1">
-      <c r="A96" s="20">
-        <f t="shared" si="4"/>
         <v>93</v>
       </c>
       <c r="B96" s="21" t="s">
@@ -28410,20 +28497,21 @@
       <c r="AD96" s="27"/>
       <c r="AE96" s="27"/>
       <c r="AF96" s="27"/>
-      <c r="AG96" s="12" t="str">
+      <c r="AG96" s="27"/>
+      <c r="AH96" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2001, 2011, </v>
+      </c>
+      <c r="AI96" s="37" t="s">
+        <v>323</v>
+      </c>
+      <c r="AJ96" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="97" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2001, 2011, </v>
-      </c>
-      <c r="AH96" s="37" t="s">
-        <v>323</v>
-      </c>
-      <c r="AI96" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="97" spans="1:35" s="3" customFormat="1">
-      <c r="A97" s="20">
-        <f t="shared" si="4"/>
         <v>94</v>
       </c>
       <c r="B97" s="21" t="s">
@@ -28511,20 +28599,21 @@
       <c r="AD97" s="27"/>
       <c r="AE97" s="27"/>
       <c r="AF97" s="27"/>
-      <c r="AG97" s="12" t="str">
+      <c r="AG97" s="27"/>
+      <c r="AH97" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2004, </v>
+      </c>
+      <c r="AI97" s="37" t="s">
+        <v>324</v>
+      </c>
+      <c r="AJ97" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="98" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2004, </v>
-      </c>
-      <c r="AH97" s="37" t="s">
-        <v>324</v>
-      </c>
-      <c r="AI97" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="98" spans="1:35" s="3" customFormat="1">
-      <c r="A98" s="20">
-        <f t="shared" si="4"/>
         <v>95</v>
       </c>
       <c r="B98" s="21" t="s">
@@ -28612,20 +28701,21 @@
       <c r="AD98" s="27"/>
       <c r="AE98" s="27"/>
       <c r="AF98" s="27"/>
-      <c r="AG98" s="12" t="str">
+      <c r="AG98" s="27"/>
+      <c r="AH98" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2006, </v>
+      </c>
+      <c r="AI98" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="AJ98" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="99" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2006, </v>
-      </c>
-      <c r="AH98" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="AI98" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="99" spans="1:35" s="3" customFormat="1">
-      <c r="A99" s="20">
-        <f t="shared" si="4"/>
         <v>96</v>
       </c>
       <c r="B99" s="21" t="s">
@@ -28713,20 +28803,21 @@
       <c r="AD99" s="27"/>
       <c r="AE99" s="27"/>
       <c r="AF99" s="27"/>
-      <c r="AG99" s="12" t="str">
+      <c r="AG99" s="27"/>
+      <c r="AH99" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2000, 2010, </v>
+      </c>
+      <c r="AI99" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="AJ99" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="100" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2000, 2010, </v>
-      </c>
-      <c r="AH99" s="37" t="s">
-        <v>326</v>
-      </c>
-      <c r="AI99" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="100" spans="1:35" s="3" customFormat="1">
-      <c r="A100" s="20">
-        <f t="shared" si="4"/>
         <v>97</v>
       </c>
       <c r="B100" s="21" t="s">
@@ -28814,20 +28905,21 @@
       <c r="AD100" s="27"/>
       <c r="AE100" s="27"/>
       <c r="AF100" s="27"/>
-      <c r="AG100" s="12" t="str">
+      <c r="AG100" s="27"/>
+      <c r="AH100" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2015, 2020, </v>
+      </c>
+      <c r="AI100" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="AJ100" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2015, 2020, </v>
-      </c>
-      <c r="AH100" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="AI100" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="101" spans="1:35" s="3" customFormat="1">
-      <c r="A101" s="20">
-        <f t="shared" si="4"/>
         <v>98</v>
       </c>
       <c r="B101" s="21" t="s">
@@ -28915,20 +29007,21 @@
       <c r="AD101" s="27"/>
       <c r="AE101" s="27"/>
       <c r="AF101" s="27"/>
-      <c r="AG101" s="12" t="str">
+      <c r="AG101" s="27"/>
+      <c r="AH101" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2001, 2011, </v>
+      </c>
+      <c r="AI101" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="AJ101" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="102" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2001, 2011, </v>
-      </c>
-      <c r="AH101" s="37" t="s">
-        <v>328</v>
-      </c>
-      <c r="AI101" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="102" spans="1:35" s="3" customFormat="1">
-      <c r="A102" s="20">
-        <f t="shared" si="4"/>
         <v>99</v>
       </c>
       <c r="B102" s="23" t="s">
@@ -29016,20 +29109,21 @@
       <c r="AD102" s="27"/>
       <c r="AE102" s="27"/>
       <c r="AF102" s="27"/>
-      <c r="AG102" s="12" t="str">
+      <c r="AG102" s="27"/>
+      <c r="AH102" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI102" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="AJ102" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="103" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="20">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AH102" s="37" t="s">
-        <v>329</v>
-      </c>
-      <c r="AI102" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="103" spans="1:35" s="3" customFormat="1">
-      <c r="A103" s="20">
-        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="B103" s="21" t="s">
@@ -29119,20 +29213,21 @@
       </c>
       <c r="AE103" s="27"/>
       <c r="AF103" s="27"/>
-      <c r="AG103" s="12" t="str">
+      <c r="AG103" s="27"/>
+      <c r="AH103" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2008, 2022, </v>
+      </c>
+      <c r="AI103" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="AJ103" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="104" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2008, 2022, </v>
-      </c>
-      <c r="AH103" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="AI103" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="104" spans="1:35" s="3" customFormat="1">
-      <c r="A104" s="20">
-        <f t="shared" si="4"/>
         <v>101</v>
       </c>
       <c r="B104" s="21" t="s">
@@ -29220,20 +29315,21 @@
       <c r="AD104" s="27"/>
       <c r="AE104" s="27"/>
       <c r="AF104" s="27"/>
-      <c r="AG104" s="12" t="str">
+      <c r="AG104" s="27"/>
+      <c r="AH104" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2012, </v>
+      </c>
+      <c r="AI104" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="AJ104" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="105" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2012, </v>
-      </c>
-      <c r="AH104" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="AI104" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="105" spans="1:35" s="3" customFormat="1">
-      <c r="A105" s="20">
-        <f t="shared" si="4"/>
         <v>102</v>
       </c>
       <c r="B105" s="21" t="s">
@@ -29321,20 +29417,21 @@
       <c r="AD105" s="27"/>
       <c r="AE105" s="27"/>
       <c r="AF105" s="27"/>
-      <c r="AG105" s="12" t="str">
+      <c r="AG105" s="27"/>
+      <c r="AH105" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2002, 2012, </v>
+      </c>
+      <c r="AI105" s="37" t="s">
+        <v>332</v>
+      </c>
+      <c r="AJ105" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="106" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2002, 2012, </v>
-      </c>
-      <c r="AH105" s="37" t="s">
-        <v>332</v>
-      </c>
-      <c r="AI105" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="106" spans="1:35" s="3" customFormat="1">
-      <c r="A106" s="20">
-        <f t="shared" si="4"/>
         <v>103</v>
       </c>
       <c r="B106" s="21" t="s">
@@ -29422,20 +29519,21 @@
       <c r="AD106" s="27"/>
       <c r="AE106" s="27"/>
       <c r="AF106" s="27"/>
-      <c r="AG106" s="12" t="str">
+      <c r="AG106" s="27"/>
+      <c r="AH106" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2002, 2010, 2020, </v>
+      </c>
+      <c r="AI106" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="AJ106" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="107" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2002, 2010, 2020, </v>
-      </c>
-      <c r="AH106" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="AI106" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="107" spans="1:35" s="3" customFormat="1">
-      <c r="A107" s="20">
-        <f t="shared" si="4"/>
         <v>104</v>
       </c>
       <c r="B107" s="23" t="s">
@@ -29523,20 +29621,21 @@
       <c r="AD107" s="27"/>
       <c r="AE107" s="27"/>
       <c r="AF107" s="27"/>
-      <c r="AG107" s="12" t="str">
+      <c r="AG107" s="27"/>
+      <c r="AH107" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2002, 2010, 2020, </v>
+      </c>
+      <c r="AI107" s="37" t="s">
+        <v>334</v>
+      </c>
+      <c r="AJ107" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="108" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2002, 2010, 2020, </v>
-      </c>
-      <c r="AH107" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="AI107" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="108" spans="1:35" s="3" customFormat="1">
-      <c r="A108" s="20">
-        <f t="shared" si="4"/>
         <v>105</v>
       </c>
       <c r="B108" s="21" t="s">
@@ -29624,20 +29723,21 @@
       <c r="AD108" s="27"/>
       <c r="AE108" s="27"/>
       <c r="AF108" s="27"/>
-      <c r="AG108" s="12" t="str">
+      <c r="AG108" s="27"/>
+      <c r="AH108" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2006, 2016, </v>
+      </c>
+      <c r="AI108" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="AJ108" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="109" spans="1:36" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2006, 2016, </v>
-      </c>
-      <c r="AH108" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="AI108" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="109" spans="1:35" s="3" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A109" s="20">
-        <f t="shared" si="4"/>
         <v>106</v>
       </c>
       <c r="B109" s="21" t="s">
@@ -29727,20 +29827,21 @@
       </c>
       <c r="AE109" s="27"/>
       <c r="AF109" s="27"/>
-      <c r="AG109" s="12" t="str">
+      <c r="AG109" s="27"/>
+      <c r="AH109" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2022, </v>
+      </c>
+      <c r="AI109" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="AJ109" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="110" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2022, </v>
-      </c>
-      <c r="AH109" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="AI109" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="110" spans="1:35" s="3" customFormat="1">
-      <c r="A110" s="20">
-        <f t="shared" si="4"/>
         <v>107</v>
       </c>
       <c r="B110" s="21" t="s">
@@ -29828,20 +29929,21 @@
       <c r="AD110" s="27"/>
       <c r="AE110" s="27"/>
       <c r="AF110" s="27"/>
-      <c r="AG110" s="12" t="str">
+      <c r="AG110" s="27"/>
+      <c r="AH110" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">1999, 2009, 2019, </v>
+      </c>
+      <c r="AI110" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="AJ110" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="111" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">1999, 2009, 2019, </v>
-      </c>
-      <c r="AH110" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="AI110" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="111" spans="1:35" s="3" customFormat="1">
-      <c r="A111" s="20">
-        <f t="shared" si="4"/>
         <v>108</v>
       </c>
       <c r="B111" s="21" t="s">
@@ -29929,20 +30031,21 @@
       <c r="AD111" s="27"/>
       <c r="AE111" s="27"/>
       <c r="AF111" s="27"/>
-      <c r="AG111" s="12" t="str">
+      <c r="AG111" s="27"/>
+      <c r="AH111" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI111" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="AJ111" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="112" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="20">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AH111" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="AI111" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="112" spans="1:35" s="3" customFormat="1">
-      <c r="A112" s="20">
-        <f t="shared" si="4"/>
         <v>109</v>
       </c>
       <c r="B112" s="21" t="s">
@@ -30032,20 +30135,21 @@
         <v>1</v>
       </c>
       <c r="AF112" s="27"/>
-      <c r="AG112" s="12" t="str">
+      <c r="AG112" s="27"/>
+      <c r="AH112" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">1999, 2013, 2023, </v>
+      </c>
+      <c r="AI112" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="AJ112" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="113" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">1999, 2013, 2023, </v>
-      </c>
-      <c r="AH112" s="37" t="s">
-        <v>339</v>
-      </c>
-      <c r="AI112" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="113" spans="1:35" s="3" customFormat="1">
-      <c r="A113" s="20">
-        <f t="shared" si="4"/>
         <v>110</v>
       </c>
       <c r="B113" s="23" t="s">
@@ -30135,20 +30239,21 @@
         <v>1</v>
       </c>
       <c r="AF113" s="27"/>
-      <c r="AG113" s="12" t="str">
+      <c r="AG113" s="27"/>
+      <c r="AH113" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2002, 2012, 2023, </v>
+      </c>
+      <c r="AI113" s="37" t="s">
+        <v>340</v>
+      </c>
+      <c r="AJ113" s="9" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="114" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2002, 2012, 2023, </v>
-      </c>
-      <c r="AH113" s="37" t="s">
-        <v>340</v>
-      </c>
-      <c r="AI113" s="9" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="114" spans="1:35" s="3" customFormat="1">
-      <c r="A114" s="20">
-        <f t="shared" si="4"/>
         <v>111</v>
       </c>
       <c r="B114" s="21" t="s">
@@ -30236,20 +30341,21 @@
       <c r="AD114" s="27"/>
       <c r="AE114" s="27"/>
       <c r="AF114" s="27"/>
-      <c r="AG114" s="12" t="str">
+      <c r="AG114" s="27"/>
+      <c r="AH114" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2002, 2011, </v>
+      </c>
+      <c r="AI114" s="37" t="s">
+        <v>342</v>
+      </c>
+      <c r="AJ114" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="115" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2002, 2011, </v>
-      </c>
-      <c r="AH114" s="37" t="s">
-        <v>342</v>
-      </c>
-      <c r="AI114" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="115" spans="1:35" s="3" customFormat="1">
-      <c r="A115" s="20">
-        <f t="shared" si="4"/>
         <v>112</v>
       </c>
       <c r="B115" s="23" t="s">
@@ -30337,20 +30443,21 @@
       <c r="AD115" s="27"/>
       <c r="AE115" s="27"/>
       <c r="AF115" s="27"/>
-      <c r="AG115" s="12" t="str">
+      <c r="AG115" s="27"/>
+      <c r="AH115" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI115" s="37" t="s">
+        <v>343</v>
+      </c>
+      <c r="AJ115" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="116" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="20">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AH115" s="37" t="s">
-        <v>343</v>
-      </c>
-      <c r="AI115" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="116" spans="1:35" s="3" customFormat="1">
-      <c r="A116" s="20">
-        <f t="shared" si="4"/>
         <v>113</v>
       </c>
       <c r="B116" s="22" t="s">
@@ -30438,20 +30545,21 @@
       <c r="AD116" s="27"/>
       <c r="AE116" s="27"/>
       <c r="AF116" s="27"/>
-      <c r="AG116" s="12" t="str">
+      <c r="AG116" s="27"/>
+      <c r="AH116" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI116" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="AJ116" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="117" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="20">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AH116" s="37" t="s">
-        <v>344</v>
-      </c>
-      <c r="AI116" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="117" spans="1:35" s="3" customFormat="1">
-      <c r="A117" s="20">
-        <f t="shared" si="4"/>
         <v>114</v>
       </c>
       <c r="B117" s="21" t="s">
@@ -30539,20 +30647,21 @@
       <c r="AD117" s="27"/>
       <c r="AE117" s="27"/>
       <c r="AF117" s="27"/>
-      <c r="AG117" s="12" t="str">
+      <c r="AG117" s="27"/>
+      <c r="AH117" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI117" s="37" t="s">
+        <v>345</v>
+      </c>
+      <c r="AJ117" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="118" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="20">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AH117" s="37" t="s">
-        <v>345</v>
-      </c>
-      <c r="AI117" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="118" spans="1:35" s="3" customFormat="1">
-      <c r="A118" s="20">
-        <f t="shared" si="4"/>
         <v>115</v>
       </c>
       <c r="B118" s="21" t="s">
@@ -30640,20 +30749,21 @@
       <c r="AD118" s="27"/>
       <c r="AE118" s="27"/>
       <c r="AF118" s="27"/>
-      <c r="AG118" s="12" t="str">
+      <c r="AG118" s="27"/>
+      <c r="AH118" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2000, 2007, 2018, </v>
+      </c>
+      <c r="AI118" s="37" t="s">
+        <v>346</v>
+      </c>
+      <c r="AJ118" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="119" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2000, 2007, 2018, </v>
-      </c>
-      <c r="AH118" s="37" t="s">
-        <v>346</v>
-      </c>
-      <c r="AI118" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="119" spans="1:35" s="3" customFormat="1">
-      <c r="A119" s="20">
-        <f t="shared" si="4"/>
         <v>116</v>
       </c>
       <c r="B119" s="23" t="s">
@@ -30741,20 +30851,21 @@
       <c r="AD119" s="27"/>
       <c r="AE119" s="27"/>
       <c r="AF119" s="27"/>
-      <c r="AG119" s="12" t="str">
+      <c r="AG119" s="27"/>
+      <c r="AH119" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI119" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="AJ119" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="120" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="20">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AH119" s="37" t="s">
-        <v>347</v>
-      </c>
-      <c r="AI119" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="120" spans="1:35" s="3" customFormat="1">
-      <c r="A120" s="20">
-        <f t="shared" si="4"/>
         <v>117</v>
       </c>
       <c r="B120" s="21" t="s">
@@ -30842,20 +30953,21 @@
       <c r="AD120" s="27"/>
       <c r="AE120" s="27"/>
       <c r="AF120" s="27"/>
-      <c r="AG120" s="12" t="str">
+      <c r="AG120" s="27"/>
+      <c r="AH120" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2002, 2013, </v>
+      </c>
+      <c r="AI120" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="AJ120" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="121" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2002, 2013, </v>
-      </c>
-      <c r="AH120" s="37" t="s">
-        <v>348</v>
-      </c>
-      <c r="AI120" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="121" spans="1:35" s="3" customFormat="1">
-      <c r="A121" s="20">
-        <f t="shared" si="4"/>
         <v>118</v>
       </c>
       <c r="B121" s="23" t="s">
@@ -30943,20 +31055,21 @@
       <c r="AD121" s="27"/>
       <c r="AE121" s="27"/>
       <c r="AF121" s="27"/>
-      <c r="AG121" s="12" t="str">
+      <c r="AG121" s="27"/>
+      <c r="AH121" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2000, </v>
+      </c>
+      <c r="AI121" s="37" t="s">
+        <v>349</v>
+      </c>
+      <c r="AJ121" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="122" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2000, </v>
-      </c>
-      <c r="AH121" s="37" t="s">
-        <v>349</v>
-      </c>
-      <c r="AI121" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="122" spans="1:35" s="3" customFormat="1">
-      <c r="A122" s="20">
-        <f t="shared" si="4"/>
         <v>119</v>
       </c>
       <c r="B122" s="23" t="s">
@@ -31044,20 +31157,21 @@
       <c r="AD122" s="27"/>
       <c r="AE122" s="27"/>
       <c r="AF122" s="27"/>
-      <c r="AG122" s="12" t="str">
+      <c r="AG122" s="27"/>
+      <c r="AH122" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">1996, 2007, </v>
+      </c>
+      <c r="AI122" s="37" t="s">
+        <v>350</v>
+      </c>
+      <c r="AJ122" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="123" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">1996, 2007, </v>
-      </c>
-      <c r="AH122" s="37" t="s">
-        <v>350</v>
-      </c>
-      <c r="AI122" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="123" spans="1:35" s="3" customFormat="1">
-      <c r="A123" s="20">
-        <f t="shared" si="4"/>
         <v>120</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -31145,20 +31259,21 @@
       <c r="AD123" s="27"/>
       <c r="AE123" s="27"/>
       <c r="AF123" s="27"/>
-      <c r="AG123" s="12" t="str">
+      <c r="AG123" s="27"/>
+      <c r="AH123" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2000, </v>
+      </c>
+      <c r="AI123" s="37" t="s">
+        <v>351</v>
+      </c>
+      <c r="AJ123" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="124" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2000, </v>
-      </c>
-      <c r="AH123" s="37" t="s">
-        <v>351</v>
-      </c>
-      <c r="AI123" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="124" spans="1:35" s="3" customFormat="1">
-      <c r="A124" s="20">
-        <f t="shared" si="4"/>
         <v>121</v>
       </c>
       <c r="B124" s="21" t="s">
@@ -31246,20 +31361,21 @@
       <c r="AD124" s="27"/>
       <c r="AE124" s="27"/>
       <c r="AF124" s="27"/>
-      <c r="AG124" s="12" t="str">
+      <c r="AG124" s="27"/>
+      <c r="AH124" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI124" s="37" t="s">
+        <v>352</v>
+      </c>
+      <c r="AJ124" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="125" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="20">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AH124" s="37" t="s">
-        <v>352</v>
-      </c>
-      <c r="AI124" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="125" spans="1:35" s="3" customFormat="1">
-      <c r="A125" s="20">
-        <f t="shared" si="4"/>
         <v>122</v>
       </c>
       <c r="B125" s="21" t="s">
@@ -31347,20 +31463,21 @@
       <c r="AD125" s="27"/>
       <c r="AE125" s="27"/>
       <c r="AF125" s="27"/>
-      <c r="AG125" s="12" t="str">
+      <c r="AG125" s="27"/>
+      <c r="AH125" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2008, </v>
+      </c>
+      <c r="AI125" s="37" t="s">
+        <v>353</v>
+      </c>
+      <c r="AJ125" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="126" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2008, </v>
-      </c>
-      <c r="AH125" s="37" t="s">
-        <v>353</v>
-      </c>
-      <c r="AI125" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="126" spans="1:35" s="3" customFormat="1">
-      <c r="A126" s="20">
-        <f t="shared" si="4"/>
         <v>123</v>
       </c>
       <c r="B126" s="23" t="s">
@@ -31448,20 +31565,21 @@
       <c r="AD126" s="27"/>
       <c r="AE126" s="27"/>
       <c r="AF126" s="27"/>
-      <c r="AG126" s="12" t="str">
+      <c r="AG126" s="27"/>
+      <c r="AH126" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AI126" s="37" t="s">
+        <v>354</v>
+      </c>
+      <c r="AJ126" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="127" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="20">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AH126" s="37" t="s">
-        <v>354</v>
-      </c>
-      <c r="AI126" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="127" spans="1:35" s="3" customFormat="1">
-      <c r="A127" s="20">
-        <f t="shared" si="4"/>
         <v>124</v>
       </c>
       <c r="B127" s="23" t="s">
@@ -31549,20 +31667,21 @@
       <c r="AD127" s="27"/>
       <c r="AE127" s="27"/>
       <c r="AF127" s="27"/>
-      <c r="AG127" s="12" t="str">
+      <c r="AG127" s="27"/>
+      <c r="AH127" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2013, </v>
+      </c>
+      <c r="AI127" s="37" t="s">
+        <v>355</v>
+      </c>
+      <c r="AJ127" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="128" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2013, </v>
-      </c>
-      <c r="AH127" s="37" t="s">
-        <v>355</v>
-      </c>
-      <c r="AI127" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="128" spans="1:35" s="3" customFormat="1">
-      <c r="A128" s="20">
-        <f t="shared" si="4"/>
         <v>125</v>
       </c>
       <c r="B128" s="23" t="s">
@@ -31650,20 +31769,21 @@
       <c r="AD128" s="27"/>
       <c r="AE128" s="27"/>
       <c r="AF128" s="27"/>
-      <c r="AG128" s="12" t="str">
+      <c r="AG128" s="27"/>
+      <c r="AH128" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2002, 2007, 2019, </v>
+      </c>
+      <c r="AI128" s="37" t="s">
+        <v>356</v>
+      </c>
+      <c r="AJ128" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="129" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2002, 2007, 2019, </v>
-      </c>
-      <c r="AH128" s="37" t="s">
-        <v>356</v>
-      </c>
-      <c r="AI128" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="129" spans="1:35" s="3" customFormat="1">
-      <c r="A129" s="20">
-        <f t="shared" si="4"/>
         <v>126</v>
       </c>
       <c r="B129" s="23" t="s">
@@ -31751,20 +31871,21 @@
       <c r="AD129" s="27"/>
       <c r="AE129" s="27"/>
       <c r="AF129" s="27"/>
-      <c r="AG129" s="12" t="str">
+      <c r="AG129" s="27"/>
+      <c r="AH129" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2003, 2013, </v>
+      </c>
+      <c r="AI129" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ129" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="130" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2003, 2013, </v>
-      </c>
-      <c r="AH129" s="37" t="s">
-        <v>357</v>
-      </c>
-      <c r="AI129" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="130" spans="1:35" s="3" customFormat="1">
-      <c r="A130" s="20">
-        <f t="shared" si="4"/>
         <v>127</v>
       </c>
       <c r="B130" s="23" t="s">
@@ -31852,20 +31973,21 @@
       <c r="AD130" s="27"/>
       <c r="AE130" s="27"/>
       <c r="AF130" s="27"/>
-      <c r="AG130" s="12" t="str">
+      <c r="AG130" s="27"/>
+      <c r="AH130" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2019, </v>
+      </c>
+      <c r="AI130" s="37" t="s">
+        <v>358</v>
+      </c>
+      <c r="AJ130" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="131" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">2019, </v>
-      </c>
-      <c r="AH130" s="37" t="s">
-        <v>358</v>
-      </c>
-      <c r="AI130" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="131" spans="1:35" s="3" customFormat="1">
-      <c r="A131" s="20">
-        <f t="shared" si="4"/>
         <v>128</v>
       </c>
       <c r="B131" s="23" t="s">
@@ -31953,20 +32075,21 @@
       <c r="AD131" s="27"/>
       <c r="AE131" s="27"/>
       <c r="AF131" s="27"/>
-      <c r="AG131" s="12" t="str">
+      <c r="AG131" s="27"/>
+      <c r="AH131" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">1996, 2012, </v>
+      </c>
+      <c r="AI131" s="37" t="s">
+        <v>359</v>
+      </c>
+      <c r="AJ131" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="132" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="20">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">1996, 2012, </v>
-      </c>
-      <c r="AH131" s="37" t="s">
-        <v>359</v>
-      </c>
-      <c r="AI131" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="132" spans="1:35" s="3" customFormat="1">
-      <c r="A132" s="20">
-        <f t="shared" si="4"/>
         <v>129</v>
       </c>
       <c r="B132" s="23" t="s">
@@ -32054,20 +32177,21 @@
       <c r="AD132" s="27"/>
       <c r="AE132" s="27"/>
       <c r="AF132" s="27"/>
-      <c r="AG132" s="12" t="str">
-        <f t="shared" ref="AG132:AG193" si="5">+IF($D132=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E132=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F132=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G132=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H132=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I132=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J132=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K132=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L132=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M132=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N132=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O132=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P132=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q132=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R132=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S132=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T132=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U132=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V132=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W132=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X132=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y132=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z132=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA132=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB132=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC132=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD132=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE132=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF132=1, RIGHT(AF$3,4)&amp;", ", "")</f>
+      <c r="AG132" s="27"/>
+      <c r="AH132" s="12" t="str">
+        <f t="shared" si="4"/>
         <v xml:space="preserve">2001, 2015, </v>
       </c>
-      <c r="AH132" s="37" t="s">
+      <c r="AI132" s="37" t="s">
         <v>360</v>
       </c>
-      <c r="AI132" s="42" t="s">
+      <c r="AJ132" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="133" spans="1:35" s="3" customFormat="1">
+    <row r="133" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="20">
-        <f t="shared" ref="A133:A193" si="6">1+A132</f>
+        <f t="shared" ref="A133:A193" si="5">1+A132</f>
         <v>130</v>
       </c>
       <c r="B133" s="23" t="s">
@@ -32155,20 +32279,21 @@
       <c r="AD133" s="27"/>
       <c r="AE133" s="27"/>
       <c r="AF133" s="27"/>
-      <c r="AG133" s="12" t="str">
+      <c r="AG133" s="27"/>
+      <c r="AH133" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2004, </v>
+      </c>
+      <c r="AI133" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="AJ133" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="134" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2004, </v>
-      </c>
-      <c r="AH133" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="AI133" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="134" spans="1:35" s="3" customFormat="1">
-      <c r="A134" s="20">
-        <f t="shared" si="6"/>
         <v>131</v>
       </c>
       <c r="B134" s="21" t="s">
@@ -32256,20 +32381,21 @@
       <c r="AD134" s="27"/>
       <c r="AE134" s="27"/>
       <c r="AF134" s="27"/>
-      <c r="AG134" s="12" t="str">
+      <c r="AG134" s="27"/>
+      <c r="AH134" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2005, </v>
+      </c>
+      <c r="AI134" s="37" t="s">
+        <v>362</v>
+      </c>
+      <c r="AJ134" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="135" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2005, </v>
-      </c>
-      <c r="AH134" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="AI134" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="135" spans="1:35" s="3" customFormat="1">
-      <c r="A135" s="20">
-        <f t="shared" si="6"/>
         <v>132</v>
       </c>
       <c r="B135" s="21" t="s">
@@ -32357,20 +32483,21 @@
       <c r="AD135" s="27"/>
       <c r="AE135" s="27"/>
       <c r="AF135" s="27"/>
-      <c r="AG135" s="12" t="str">
+      <c r="AG135" s="27"/>
+      <c r="AH135" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2001, </v>
+      </c>
+      <c r="AI135" s="37" t="s">
+        <v>363</v>
+      </c>
+      <c r="AJ135" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="136" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2001, </v>
-      </c>
-      <c r="AH135" s="37" t="s">
-        <v>363</v>
-      </c>
-      <c r="AI135" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="136" spans="1:35" s="3" customFormat="1">
-      <c r="A136" s="20">
-        <f t="shared" si="6"/>
         <v>133</v>
       </c>
       <c r="B136" s="23" t="s">
@@ -32458,20 +32585,21 @@
       <c r="AD136" s="27"/>
       <c r="AE136" s="27"/>
       <c r="AF136" s="27"/>
-      <c r="AG136" s="12" t="str">
+      <c r="AG136" s="27"/>
+      <c r="AH136" s="12" t="str">
+        <f t="shared" ref="AH136:AH193" si="6">+IF($D136=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E136=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F136=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G136=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H136=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I136=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J136=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K136=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L136=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M136=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N136=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O136=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P136=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q136=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R136=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S136=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T136=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U136=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V136=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W136=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X136=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y136=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z136=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA136=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB136=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC136=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD136=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE136=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF136=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG136=1, RIGHT(AG$3,4)&amp;", ", "")</f>
+        <v/>
+      </c>
+      <c r="AI136" s="37" t="s">
+        <v>364</v>
+      </c>
+      <c r="AJ136" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="137" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="20">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AH136" s="37" t="s">
-        <v>364</v>
-      </c>
-      <c r="AI136" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="137" spans="1:35" s="3" customFormat="1">
-      <c r="A137" s="20">
-        <f t="shared" si="6"/>
         <v>134</v>
       </c>
       <c r="B137" s="23" t="s">
@@ -32559,20 +32687,21 @@
       <c r="AD137" s="27"/>
       <c r="AE137" s="27"/>
       <c r="AF137" s="27"/>
-      <c r="AG137" s="12" t="str">
+      <c r="AG137" s="27"/>
+      <c r="AH137" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2017, </v>
+      </c>
+      <c r="AI137" s="37" t="s">
+        <v>365</v>
+      </c>
+      <c r="AJ137" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="138" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2017, </v>
-      </c>
-      <c r="AH137" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="AI137" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="138" spans="1:35" s="3" customFormat="1">
-      <c r="A138" s="20">
-        <f t="shared" si="6"/>
         <v>135</v>
       </c>
       <c r="B138" s="23" t="s">
@@ -32660,20 +32789,21 @@
       <c r="AD138" s="27"/>
       <c r="AE138" s="27"/>
       <c r="AF138" s="27"/>
-      <c r="AG138" s="12" t="str">
+      <c r="AG138" s="27"/>
+      <c r="AH138" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2008, </v>
+      </c>
+      <c r="AI138" s="37" t="s">
+        <v>366</v>
+      </c>
+      <c r="AJ138" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="139" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2008, </v>
-      </c>
-      <c r="AH138" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="AI138" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="139" spans="1:35" s="3" customFormat="1">
-      <c r="A139" s="20">
-        <f t="shared" si="6"/>
         <v>136</v>
       </c>
       <c r="B139" s="23" t="s">
@@ -32761,20 +32891,21 @@
       <c r="AD139" s="27"/>
       <c r="AE139" s="27"/>
       <c r="AF139" s="27"/>
-      <c r="AG139" s="12" t="str">
+      <c r="AG139" s="27"/>
+      <c r="AH139" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AI139" s="37" t="s">
+        <v>367</v>
+      </c>
+      <c r="AJ139" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="140" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="20">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AH139" s="37" t="s">
-        <v>367</v>
-      </c>
-      <c r="AI139" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="140" spans="1:35" s="3" customFormat="1">
-      <c r="A140" s="20">
-        <f t="shared" si="6"/>
         <v>137</v>
       </c>
       <c r="B140" s="25" t="s">
@@ -32862,20 +32993,21 @@
       <c r="AD140" s="27"/>
       <c r="AE140" s="27"/>
       <c r="AF140" s="27"/>
-      <c r="AG140" s="12" t="str">
+      <c r="AG140" s="27"/>
+      <c r="AH140" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2000, 2011, </v>
+      </c>
+      <c r="AI140" s="37" t="s">
+        <v>368</v>
+      </c>
+      <c r="AJ140" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="141" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2000, 2011, </v>
-      </c>
-      <c r="AH140" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="AI140" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="141" spans="1:35" s="3" customFormat="1">
-      <c r="A141" s="20">
-        <f t="shared" si="6"/>
         <v>138</v>
       </c>
       <c r="B141" s="23" t="s">
@@ -32963,20 +33095,21 @@
       <c r="AD141" s="27"/>
       <c r="AE141" s="27"/>
       <c r="AF141" s="27"/>
-      <c r="AG141" s="12" t="str">
+      <c r="AG141" s="27"/>
+      <c r="AH141" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AI141" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="AJ141" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="142" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="20">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AH141" s="37" t="s">
-        <v>369</v>
-      </c>
-      <c r="AI141" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="142" spans="1:35" s="3" customFormat="1">
-      <c r="A142" s="20">
-        <f t="shared" si="6"/>
         <v>139</v>
       </c>
       <c r="B142" s="25" t="s">
@@ -33064,20 +33197,21 @@
       <c r="AD142" s="27"/>
       <c r="AE142" s="27"/>
       <c r="AF142" s="27"/>
-      <c r="AG142" s="12" t="str">
+      <c r="AG142" s="27"/>
+      <c r="AH142" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2007, </v>
+      </c>
+      <c r="AI142" s="37" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ142" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="143" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2007, </v>
-      </c>
-      <c r="AH142" s="37" t="s">
-        <v>370</v>
-      </c>
-      <c r="AI142" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="143" spans="1:35" s="3" customFormat="1">
-      <c r="A143" s="20">
-        <f t="shared" si="6"/>
         <v>140</v>
       </c>
       <c r="B143" s="25" t="s">
@@ -33165,20 +33299,21 @@
       <c r="AD143" s="27"/>
       <c r="AE143" s="27"/>
       <c r="AF143" s="27"/>
-      <c r="AG143" s="12" t="str">
+      <c r="AG143" s="27"/>
+      <c r="AH143" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1996, 2008, </v>
+      </c>
+      <c r="AI143" s="37" t="s">
+        <v>371</v>
+      </c>
+      <c r="AJ143" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="144" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1996, 2008, </v>
-      </c>
-      <c r="AH143" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="AI143" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="144" spans="1:35" s="3" customFormat="1">
-      <c r="A144" s="20">
-        <f t="shared" si="6"/>
         <v>141</v>
       </c>
       <c r="B144" s="25" t="s">
@@ -33266,20 +33401,21 @@
       <c r="AD144" s="27"/>
       <c r="AE144" s="27"/>
       <c r="AF144" s="27"/>
-      <c r="AG144" s="12" t="str">
+      <c r="AG144" s="27"/>
+      <c r="AH144" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2001, 2006, 2011, 2016, 2020, </v>
+      </c>
+      <c r="AI144" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="AJ144" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="145" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2001, 2006, 2011, 2016, 2020, </v>
-      </c>
-      <c r="AH144" s="37" t="s">
-        <v>372</v>
-      </c>
-      <c r="AI144" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="145" spans="1:35" s="3" customFormat="1">
-      <c r="A145" s="20">
-        <f t="shared" si="6"/>
         <v>142</v>
       </c>
       <c r="B145" s="21" t="s">
@@ -33369,20 +33505,21 @@
       <c r="AD145" s="27"/>
       <c r="AE145" s="27"/>
       <c r="AF145" s="27"/>
-      <c r="AG145" s="12" t="str">
+      <c r="AG145" s="27"/>
+      <c r="AH145" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2010, 2021, </v>
+      </c>
+      <c r="AI145" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="AJ145" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="146" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2010, 2021, </v>
-      </c>
-      <c r="AH145" s="37" t="s">
-        <v>373</v>
-      </c>
-      <c r="AI145" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="146" spans="1:35" s="3" customFormat="1">
-      <c r="A146" s="20">
-        <f t="shared" si="6"/>
         <v>143</v>
       </c>
       <c r="B146" s="25" t="s">
@@ -33470,20 +33607,21 @@
       <c r="AD146" s="27"/>
       <c r="AE146" s="27"/>
       <c r="AF146" s="27"/>
-      <c r="AG146" s="12" t="str">
+      <c r="AG146" s="27"/>
+      <c r="AH146" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2002, </v>
+      </c>
+      <c r="AI146" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="AJ146" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="147" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2002, </v>
-      </c>
-      <c r="AH146" s="37" t="s">
-        <v>374</v>
-      </c>
-      <c r="AI146" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="147" spans="1:35" s="3" customFormat="1">
-      <c r="A147" s="20">
-        <f t="shared" si="6"/>
         <v>144</v>
       </c>
       <c r="B147" s="25" t="s">
@@ -33571,20 +33709,21 @@
       <c r="AD147" s="27"/>
       <c r="AE147" s="27"/>
       <c r="AF147" s="27"/>
-      <c r="AG147" s="12" t="str">
+      <c r="AG147" s="27"/>
+      <c r="AH147" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2000, </v>
+      </c>
+      <c r="AI147" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="AJ147" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="148" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2000, </v>
-      </c>
-      <c r="AH147" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="AI147" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="148" spans="1:35" s="3" customFormat="1">
-      <c r="A148" s="20">
-        <f t="shared" si="6"/>
         <v>145</v>
       </c>
       <c r="B148" s="25" t="s">
@@ -33672,20 +33811,21 @@
       <c r="AD148" s="27"/>
       <c r="AE148" s="27"/>
       <c r="AF148" s="27"/>
-      <c r="AG148" s="12" t="str">
+      <c r="AG148" s="27"/>
+      <c r="AH148" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AI148" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="AJ148" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="149" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A149" s="20">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AH148" s="37" t="s">
-        <v>376</v>
-      </c>
-      <c r="AI148" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="149" spans="1:35">
-      <c r="A149" s="20">
-        <f t="shared" si="6"/>
         <v>146</v>
       </c>
       <c r="B149" s="14" t="s">
@@ -33773,20 +33913,21 @@
       <c r="AD149" s="39"/>
       <c r="AE149" s="39"/>
       <c r="AF149" s="39"/>
-      <c r="AG149" s="12" t="str">
+      <c r="AG149" s="39"/>
+      <c r="AH149" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AI149" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="AJ149" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="150" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A150" s="20">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AH149" s="37" t="s">
-        <v>377</v>
-      </c>
-      <c r="AI149" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="150" spans="1:35">
-      <c r="A150" s="20">
-        <f t="shared" si="6"/>
         <v>147</v>
       </c>
       <c r="B150" s="14" t="s">
@@ -33874,20 +34015,21 @@
       <c r="AD150" s="39"/>
       <c r="AE150" s="39"/>
       <c r="AF150" s="39"/>
-      <c r="AG150" s="12" t="str">
+      <c r="AG150" s="39"/>
+      <c r="AH150" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AI150" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="AJ150" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="151" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A151" s="20">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AH150" s="37" t="s">
-        <v>378</v>
-      </c>
-      <c r="AI150" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="151" spans="1:35">
-      <c r="A151" s="20">
-        <f t="shared" si="6"/>
         <v>148</v>
       </c>
       <c r="B151" s="14" t="s">
@@ -33975,20 +34117,21 @@
       <c r="AD151" s="39"/>
       <c r="AE151" s="39"/>
       <c r="AF151" s="39"/>
-      <c r="AG151" s="12" t="str">
+      <c r="AG151" s="39"/>
+      <c r="AH151" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2000, 2010, 2020, </v>
+      </c>
+      <c r="AI151" s="37" t="s">
+        <v>379</v>
+      </c>
+      <c r="AJ151" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="152" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A152" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2000, 2010, 2020, </v>
-      </c>
-      <c r="AH151" s="37" t="s">
-        <v>379</v>
-      </c>
-      <c r="AI151" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="152" spans="1:35">
-      <c r="A152" s="20">
-        <f t="shared" si="6"/>
         <v>149</v>
       </c>
       <c r="B152" s="14" t="s">
@@ -34076,20 +34219,21 @@
       <c r="AD152" s="39"/>
       <c r="AE152" s="39"/>
       <c r="AF152" s="39"/>
-      <c r="AG152" s="12" t="str">
+      <c r="AG152" s="39"/>
+      <c r="AH152" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2000, 2010, 2020, </v>
+      </c>
+      <c r="AI152" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="AJ152" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="153" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A153" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2000, 2010, 2020, </v>
-      </c>
-      <c r="AH152" s="37" t="s">
-        <v>380</v>
-      </c>
-      <c r="AI152" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="153" spans="1:35">
-      <c r="A153" s="20">
-        <f t="shared" si="6"/>
         <v>150</v>
       </c>
       <c r="B153" s="14" t="s">
@@ -34177,20 +34321,21 @@
       <c r="AD153" s="39"/>
       <c r="AE153" s="39"/>
       <c r="AF153" s="39"/>
-      <c r="AG153" s="12" t="str">
+      <c r="AG153" s="39"/>
+      <c r="AH153" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2000, 2010, 2020, </v>
+      </c>
+      <c r="AI153" s="37" t="s">
+        <v>381</v>
+      </c>
+      <c r="AJ153" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="154" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A154" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2000, 2010, 2020, </v>
-      </c>
-      <c r="AH153" s="37" t="s">
-        <v>381</v>
-      </c>
-      <c r="AI153" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="154" spans="1:35">
-      <c r="A154" s="20">
-        <f t="shared" si="6"/>
         <v>151</v>
       </c>
       <c r="B154" s="14" t="s">
@@ -34278,20 +34423,21 @@
       <c r="AD154" s="39"/>
       <c r="AE154" s="39"/>
       <c r="AF154" s="39"/>
-      <c r="AG154" s="12" t="str">
+      <c r="AG154" s="39"/>
+      <c r="AH154" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2001, 2010, 2020, </v>
+      </c>
+      <c r="AI154" s="37" t="s">
+        <v>382</v>
+      </c>
+      <c r="AJ154" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="155" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A155" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2001, 2010, 2020, </v>
-      </c>
-      <c r="AH154" s="37" t="s">
-        <v>382</v>
-      </c>
-      <c r="AI154" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="155" spans="1:35">
-      <c r="A155" s="20">
-        <f t="shared" si="6"/>
         <v>152</v>
       </c>
       <c r="B155" s="14" t="s">
@@ -34379,20 +34525,21 @@
       <c r="AD155" s="39"/>
       <c r="AE155" s="39"/>
       <c r="AF155" s="39"/>
-      <c r="AG155" s="12" t="str">
+      <c r="AG155" s="39"/>
+      <c r="AH155" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2003, 2010, 2020, </v>
+      </c>
+      <c r="AI155" s="37" t="s">
+        <v>383</v>
+      </c>
+      <c r="AJ155" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="156" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A156" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2003, 2010, 2020, </v>
-      </c>
-      <c r="AH155" s="37" t="s">
-        <v>383</v>
-      </c>
-      <c r="AI155" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="156" spans="1:35">
-      <c r="A156" s="20">
-        <f t="shared" si="6"/>
         <v>153</v>
       </c>
       <c r="B156" s="14" t="s">
@@ -34480,20 +34627,21 @@
       <c r="AD156" s="39"/>
       <c r="AE156" s="39"/>
       <c r="AF156" s="39"/>
-      <c r="AG156" s="12" t="str">
+      <c r="AG156" s="39"/>
+      <c r="AH156" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2013, </v>
+      </c>
+      <c r="AI156" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="AJ156" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="157" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A157" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2013, </v>
-      </c>
-      <c r="AH156" s="37" t="s">
-        <v>384</v>
-      </c>
-      <c r="AI156" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="157" spans="1:35">
-      <c r="A157" s="20">
-        <f t="shared" si="6"/>
         <v>154</v>
       </c>
       <c r="B157" s="14" t="s">
@@ -34581,20 +34729,21 @@
       <c r="AD157" s="39"/>
       <c r="AE157" s="39"/>
       <c r="AF157" s="39"/>
-      <c r="AG157" s="12" t="str">
+      <c r="AG157" s="39"/>
+      <c r="AH157" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1999, 2015, </v>
+      </c>
+      <c r="AI157" s="37" t="s">
+        <v>385</v>
+      </c>
+      <c r="AJ157" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="158" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A158" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1999, 2015, </v>
-      </c>
-      <c r="AH157" s="37" t="s">
-        <v>385</v>
-      </c>
-      <c r="AI157" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="158" spans="1:35">
-      <c r="A158" s="20">
-        <f t="shared" si="6"/>
         <v>155</v>
       </c>
       <c r="B158" s="14" t="s">
@@ -34682,20 +34831,21 @@
       <c r="AD158" s="39"/>
       <c r="AE158" s="39"/>
       <c r="AF158" s="39"/>
-      <c r="AG158" s="12" t="str">
+      <c r="AG158" s="39"/>
+      <c r="AH158" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2001, 2010, 2020, </v>
+      </c>
+      <c r="AI158" s="37" t="s">
+        <v>386</v>
+      </c>
+      <c r="AJ158" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="159" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A159" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2001, 2010, 2020, </v>
-      </c>
-      <c r="AH158" s="37" t="s">
-        <v>386</v>
-      </c>
-      <c r="AI158" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="159" spans="1:35">
-      <c r="A159" s="20">
-        <f t="shared" si="6"/>
         <v>156</v>
       </c>
       <c r="B159" s="14" t="s">
@@ -34783,20 +34933,21 @@
       <c r="AD159" s="40"/>
       <c r="AE159" s="40"/>
       <c r="AF159" s="40"/>
-      <c r="AG159" s="12" t="str">
+      <c r="AG159" s="40"/>
+      <c r="AH159" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AI159" s="37" t="s">
+        <v>388</v>
+      </c>
+      <c r="AJ159" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="160" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A160" s="20">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AH159" s="37" t="s">
-        <v>388</v>
-      </c>
-      <c r="AI159" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="160" spans="1:35">
-      <c r="A160" s="20">
-        <f t="shared" si="6"/>
         <v>157</v>
       </c>
       <c r="B160" s="14" t="s">
@@ -34884,20 +35035,21 @@
       <c r="AD160" s="40"/>
       <c r="AE160" s="40"/>
       <c r="AF160" s="40"/>
-      <c r="AG160" s="12" t="str">
+      <c r="AG160" s="40"/>
+      <c r="AH160" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AI160" s="37" t="s">
+        <v>389</v>
+      </c>
+      <c r="AJ160" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="161" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A161" s="20">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AH160" s="37" t="s">
-        <v>389</v>
-      </c>
-      <c r="AI160" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="161" spans="1:35">
-      <c r="A161" s="20">
-        <f t="shared" si="6"/>
         <v>158</v>
       </c>
       <c r="B161" s="14" t="s">
@@ -34985,20 +35137,21 @@
       <c r="AD161" s="39"/>
       <c r="AE161" s="39"/>
       <c r="AF161" s="39"/>
-      <c r="AG161" s="12" t="str">
+      <c r="AG161" s="39"/>
+      <c r="AH161" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2001, 2010, 2015, </v>
+      </c>
+      <c r="AI161" s="37" t="s">
+        <v>390</v>
+      </c>
+      <c r="AJ161" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="162" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A162" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2001, 2010, 2015, </v>
-      </c>
-      <c r="AH161" s="37" t="s">
-        <v>390</v>
-      </c>
-      <c r="AI161" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="162" spans="1:35">
-      <c r="A162" s="20">
-        <f t="shared" si="6"/>
         <v>159</v>
       </c>
       <c r="B162" s="14" t="s">
@@ -35086,20 +35239,21 @@
       <c r="AD162" s="39"/>
       <c r="AE162" s="39"/>
       <c r="AF162" s="39"/>
-      <c r="AG162" s="12" t="str">
+      <c r="AG162" s="39"/>
+      <c r="AH162" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1999, 2010, 2020, </v>
+      </c>
+      <c r="AI162" s="37" t="s">
+        <v>391</v>
+      </c>
+      <c r="AJ162" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="163" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A163" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1999, 2010, 2020, </v>
-      </c>
-      <c r="AH162" s="37" t="s">
-        <v>391</v>
-      </c>
-      <c r="AI162" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="163" spans="1:35">
-      <c r="A163" s="20">
-        <f t="shared" si="6"/>
         <v>160</v>
       </c>
       <c r="B163" s="14" t="s">
@@ -35187,20 +35341,21 @@
       <c r="AD163" s="39"/>
       <c r="AE163" s="39"/>
       <c r="AF163" s="39"/>
-      <c r="AG163" s="12" t="str">
+      <c r="AG163" s="39"/>
+      <c r="AH163" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1999, 2003, 2005, 2007, 2010, 2016, 2020, </v>
+      </c>
+      <c r="AI163" s="37" t="s">
+        <v>392</v>
+      </c>
+      <c r="AJ163" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="164" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A164" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1999, 2003, 2005, 2007, 2010, 2016, 2020, </v>
-      </c>
-      <c r="AH163" s="37" t="s">
-        <v>392</v>
-      </c>
-      <c r="AI163" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="164" spans="1:35">
-      <c r="A164" s="20">
-        <f t="shared" si="6"/>
         <v>161</v>
       </c>
       <c r="B164" s="14" t="s">
@@ -35288,20 +35443,21 @@
       <c r="AD164" s="39"/>
       <c r="AE164" s="39"/>
       <c r="AF164" s="39"/>
-      <c r="AG164" s="12" t="str">
+      <c r="AG164" s="39"/>
+      <c r="AH164" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AI164" s="37" t="s">
+        <v>393</v>
+      </c>
+      <c r="AJ164" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="165" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A165" s="20">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AH164" s="37" t="s">
-        <v>393</v>
-      </c>
-      <c r="AI164" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="165" spans="1:35">
-      <c r="A165" s="20">
-        <f t="shared" si="6"/>
         <v>162</v>
       </c>
       <c r="B165" s="14" t="s">
@@ -35389,20 +35545,21 @@
       <c r="AD165" s="39"/>
       <c r="AE165" s="39"/>
       <c r="AF165" s="39"/>
-      <c r="AG165" s="12" t="str">
+      <c r="AG165" s="39"/>
+      <c r="AH165" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AI165" s="37" t="s">
+        <v>394</v>
+      </c>
+      <c r="AJ165" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="166" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A166" s="20">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AH165" s="37" t="s">
-        <v>394</v>
-      </c>
-      <c r="AI165" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="166" spans="1:35">
-      <c r="A166" s="20">
-        <f t="shared" si="6"/>
         <v>163</v>
       </c>
       <c r="B166" s="14" t="s">
@@ -35492,20 +35649,21 @@
       <c r="AD166" s="39"/>
       <c r="AE166" s="39"/>
       <c r="AF166" s="39"/>
-      <c r="AG166" s="12" t="str">
+      <c r="AG166" s="39"/>
+      <c r="AH166" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2001, 2011, 2016, 2021, </v>
+      </c>
+      <c r="AI166" s="37" t="s">
+        <v>395</v>
+      </c>
+      <c r="AJ166" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="167" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A167" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2001, 2011, 2016, 2021, </v>
-      </c>
-      <c r="AH166" s="37" t="s">
-        <v>395</v>
-      </c>
-      <c r="AI166" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="167" spans="1:35">
-      <c r="A167" s="20">
-        <f t="shared" si="6"/>
         <v>164</v>
       </c>
       <c r="B167" s="14" t="s">
@@ -35593,20 +35751,21 @@
       <c r="AD167" s="39"/>
       <c r="AE167" s="39"/>
       <c r="AF167" s="39"/>
-      <c r="AG167" s="12" t="str">
+      <c r="AG167" s="39"/>
+      <c r="AH167" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2000, 2010, 2020, </v>
+      </c>
+      <c r="AI167" s="37" t="s">
+        <v>396</v>
+      </c>
+      <c r="AJ167" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="168" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A168" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2000, 2010, 2020, </v>
-      </c>
-      <c r="AH167" s="37" t="s">
-        <v>396</v>
-      </c>
-      <c r="AI167" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="168" spans="1:35">
-      <c r="A168" s="20">
-        <f t="shared" si="6"/>
         <v>165</v>
       </c>
       <c r="B168" s="14" t="s">
@@ -35694,20 +35853,21 @@
       <c r="AD168" s="39"/>
       <c r="AE168" s="39"/>
       <c r="AF168" s="39"/>
-      <c r="AG168" s="12" t="str">
+      <c r="AG168" s="39"/>
+      <c r="AH168" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2003, 2010, 2020, </v>
+      </c>
+      <c r="AI168" s="37" t="s">
+        <v>397</v>
+      </c>
+      <c r="AJ168" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A169" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2003, 2010, 2020, </v>
-      </c>
-      <c r="AH168" s="37" t="s">
-        <v>397</v>
-      </c>
-      <c r="AI168" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="169" spans="1:35">
-      <c r="A169" s="20">
-        <f t="shared" si="6"/>
         <v>166</v>
       </c>
       <c r="B169" s="14" t="s">
@@ -35795,20 +35955,21 @@
       <c r="AD169" s="39"/>
       <c r="AE169" s="39"/>
       <c r="AF169" s="39"/>
-      <c r="AG169" s="12" t="str">
+      <c r="AG169" s="39"/>
+      <c r="AH169" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1999, 2010, 2020, </v>
+      </c>
+      <c r="AI169" s="37" t="s">
+        <v>398</v>
+      </c>
+      <c r="AJ169" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="170" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A170" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1999, 2010, 2020, </v>
-      </c>
-      <c r="AH169" s="37" t="s">
-        <v>398</v>
-      </c>
-      <c r="AI169" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="170" spans="1:35">
-      <c r="A170" s="20">
-        <f t="shared" si="6"/>
         <v>167</v>
       </c>
       <c r="B170" s="14" t="s">
@@ -35896,20 +36057,21 @@
       <c r="AD170" s="39"/>
       <c r="AE170" s="39"/>
       <c r="AF170" s="39"/>
-      <c r="AG170" s="12" t="str">
+      <c r="AG170" s="39"/>
+      <c r="AH170" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1999, 2010, 2020, </v>
+      </c>
+      <c r="AI170" s="37" t="s">
+        <v>399</v>
+      </c>
+      <c r="AJ170" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="171" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A171" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1999, 2010, 2020, </v>
-      </c>
-      <c r="AH170" s="37" t="s">
-        <v>399</v>
-      </c>
-      <c r="AI170" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="171" spans="1:35">
-      <c r="A171" s="20">
-        <f t="shared" si="6"/>
         <v>168</v>
       </c>
       <c r="B171" s="14" t="s">
@@ -35997,20 +36159,21 @@
       <c r="AD171" s="39"/>
       <c r="AE171" s="39"/>
       <c r="AF171" s="39"/>
-      <c r="AG171" s="12" t="str">
+      <c r="AG171" s="39"/>
+      <c r="AH171" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1999, 2009, 2020, </v>
+      </c>
+      <c r="AI171" s="37" t="s">
+        <v>400</v>
+      </c>
+      <c r="AJ171" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="172" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A172" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1999, 2009, 2020, </v>
-      </c>
-      <c r="AH171" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="AI171" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="172" spans="1:35">
-      <c r="A172" s="20">
-        <f t="shared" si="6"/>
         <v>169</v>
       </c>
       <c r="B172" s="14" t="s">
@@ -36098,20 +36261,21 @@
       <c r="AD172" s="39"/>
       <c r="AE172" s="39"/>
       <c r="AF172" s="39"/>
-      <c r="AG172" s="12" t="str">
+      <c r="AG172" s="39"/>
+      <c r="AH172" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2001, 2010, 2020, </v>
+      </c>
+      <c r="AI172" s="37" t="s">
+        <v>401</v>
+      </c>
+      <c r="AJ172" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="173" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A173" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2001, 2010, 2020, </v>
-      </c>
-      <c r="AH172" s="37" t="s">
-        <v>401</v>
-      </c>
-      <c r="AI172" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="173" spans="1:35">
-      <c r="A173" s="20">
-        <f t="shared" si="6"/>
         <v>170</v>
       </c>
       <c r="B173" s="14" t="s">
@@ -36199,20 +36363,21 @@
       <c r="AD173" s="39"/>
       <c r="AE173" s="39"/>
       <c r="AF173" s="39"/>
-      <c r="AG173" s="12" t="str">
+      <c r="AG173" s="39"/>
+      <c r="AH173" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1999, 2010, 2020, </v>
+      </c>
+      <c r="AI173" s="37" t="s">
+        <v>402</v>
+      </c>
+      <c r="AJ173" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="174" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A174" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1999, 2010, 2020, </v>
-      </c>
-      <c r="AH173" s="37" t="s">
-        <v>402</v>
-      </c>
-      <c r="AI173" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="174" spans="1:35">
-      <c r="A174" s="20">
-        <f t="shared" si="6"/>
         <v>171</v>
       </c>
       <c r="B174" s="14" t="s">
@@ -36300,20 +36465,21 @@
       <c r="AD174" s="39"/>
       <c r="AE174" s="39"/>
       <c r="AF174" s="39"/>
-      <c r="AG174" s="12" t="str">
+      <c r="AG174" s="39"/>
+      <c r="AH174" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1999, 2010, 2020, </v>
+      </c>
+      <c r="AI174" s="37" t="s">
+        <v>403</v>
+      </c>
+      <c r="AJ174" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="175" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A175" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1999, 2010, 2020, </v>
-      </c>
-      <c r="AH174" s="37" t="s">
-        <v>403</v>
-      </c>
-      <c r="AI174" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="175" spans="1:35">
-      <c r="A175" s="20">
-        <f t="shared" si="6"/>
         <v>172</v>
       </c>
       <c r="B175" s="14" t="s">
@@ -36403,20 +36569,21 @@
       <c r="AD175" s="39"/>
       <c r="AE175" s="39"/>
       <c r="AF175" s="39"/>
-      <c r="AG175" s="12" t="str">
+      <c r="AG175" s="39"/>
+      <c r="AH175" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1999, 2010, 2021, </v>
+      </c>
+      <c r="AI175" s="37" t="s">
+        <v>404</v>
+      </c>
+      <c r="AJ175" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="176" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A176" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1999, 2010, 2021, </v>
-      </c>
-      <c r="AH175" s="37" t="s">
-        <v>404</v>
-      </c>
-      <c r="AI175" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="176" spans="1:35">
-      <c r="A176" s="20">
-        <f t="shared" si="6"/>
         <v>173</v>
       </c>
       <c r="B176" s="14" t="s">
@@ -36506,20 +36673,21 @@
       <c r="AF176" s="39">
         <v>1</v>
       </c>
-      <c r="AG176" s="12" t="str">
+      <c r="AG176" s="39"/>
+      <c r="AH176" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2000, 2010, 2020, 2024, </v>
+      </c>
+      <c r="AI176" s="37" t="s">
+        <v>405</v>
+      </c>
+      <c r="AJ176" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="177" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A177" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2000, 2010, 2020, 2024, </v>
-      </c>
-      <c r="AH176" s="37" t="s">
-        <v>405</v>
-      </c>
-      <c r="AI176" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="177" spans="1:35">
-      <c r="A177" s="20">
-        <f t="shared" si="6"/>
         <v>174</v>
       </c>
       <c r="B177" s="14" t="s">
@@ -36607,20 +36775,21 @@
       <c r="AD177" s="39"/>
       <c r="AE177" s="39"/>
       <c r="AF177" s="39"/>
-      <c r="AG177" s="12" t="str">
+      <c r="AG177" s="39"/>
+      <c r="AH177" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2010, 2020, </v>
+      </c>
+      <c r="AI177" s="37" t="s">
+        <v>406</v>
+      </c>
+      <c r="AJ177" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="178" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A178" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2010, 2020, </v>
-      </c>
-      <c r="AH177" s="37" t="s">
-        <v>406</v>
-      </c>
-      <c r="AI177" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="178" spans="1:35">
-      <c r="A178" s="20">
-        <f t="shared" si="6"/>
         <v>175</v>
       </c>
       <c r="B178" s="14" t="s">
@@ -36708,20 +36877,21 @@
       <c r="AD178" s="39"/>
       <c r="AE178" s="39"/>
       <c r="AF178" s="39"/>
-      <c r="AG178" s="12" t="str">
+      <c r="AG178" s="39"/>
+      <c r="AH178" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2017, </v>
+      </c>
+      <c r="AI178" s="37" t="s">
+        <v>407</v>
+      </c>
+      <c r="AJ178" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="179" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A179" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2017, </v>
-      </c>
-      <c r="AH178" s="37" t="s">
-        <v>407</v>
-      </c>
-      <c r="AI178" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="179" spans="1:35">
-      <c r="A179" s="20">
-        <f t="shared" si="6"/>
         <v>176</v>
       </c>
       <c r="B179" s="14" t="s">
@@ -36809,20 +36979,21 @@
       <c r="AD179" s="39"/>
       <c r="AE179" s="39"/>
       <c r="AF179" s="39"/>
-      <c r="AG179" s="12" t="str">
+      <c r="AG179" s="39"/>
+      <c r="AH179" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2000, 2010, 2020, </v>
+      </c>
+      <c r="AI179" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="AJ179" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="180" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A180" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2000, 2010, 2020, </v>
-      </c>
-      <c r="AH179" s="37" t="s">
-        <v>408</v>
-      </c>
-      <c r="AI179" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="180" spans="1:35">
-      <c r="A180" s="20">
-        <f t="shared" si="6"/>
         <v>177</v>
       </c>
       <c r="B180" s="14" t="s">
@@ -36910,20 +37081,23 @@
       <c r="AD180" s="39"/>
       <c r="AE180" s="39"/>
       <c r="AF180" s="39"/>
-      <c r="AG180" s="12" t="str">
+      <c r="AG180" s="39">
+        <v>1</v>
+      </c>
+      <c r="AH180" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2000, 2010, 2015, 2020, 2025, </v>
+      </c>
+      <c r="AI180" s="37" t="s">
+        <v>409</v>
+      </c>
+      <c r="AJ180" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="181" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A181" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2000, 2010, 2015, 2020, </v>
-      </c>
-      <c r="AH180" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="AI180" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="181" spans="1:35">
-      <c r="A181" s="20">
-        <f t="shared" si="6"/>
         <v>178</v>
       </c>
       <c r="B181" s="14" t="s">
@@ -37011,20 +37185,23 @@
       <c r="AD181" s="39"/>
       <c r="AE181" s="39"/>
       <c r="AF181" s="39"/>
-      <c r="AG181" s="12" t="str">
+      <c r="AG181" s="39">
+        <v>1</v>
+      </c>
+      <c r="AH181" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2000, 2010, 2020, 2025, </v>
+      </c>
+      <c r="AI181" s="37" t="s">
+        <v>410</v>
+      </c>
+      <c r="AJ181" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="182" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A182" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2000, 2010, 2020, </v>
-      </c>
-      <c r="AH181" s="37" t="s">
-        <v>410</v>
-      </c>
-      <c r="AI181" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="182" spans="1:35">
-      <c r="A182" s="20">
-        <f t="shared" si="6"/>
         <v>179</v>
       </c>
       <c r="B182" s="14" t="s">
@@ -37112,20 +37289,21 @@
       <c r="AD182" s="39"/>
       <c r="AE182" s="39"/>
       <c r="AF182" s="39"/>
-      <c r="AG182" s="12" t="str">
+      <c r="AG182" s="39"/>
+      <c r="AH182" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AI182" s="37" t="s">
+        <v>411</v>
+      </c>
+      <c r="AJ182" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A183" s="20">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AH182" s="37" t="s">
-        <v>411</v>
-      </c>
-      <c r="AI182" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="183" spans="1:35">
-      <c r="A183" s="20">
-        <f t="shared" si="6"/>
         <v>180</v>
       </c>
       <c r="B183" s="14" t="s">
@@ -37213,20 +37391,21 @@
       <c r="AD183" s="39"/>
       <c r="AE183" s="39"/>
       <c r="AF183" s="39"/>
-      <c r="AG183" s="12" t="str">
+      <c r="AG183" s="39"/>
+      <c r="AH183" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1999, 2010, 2020, </v>
+      </c>
+      <c r="AI183" s="37" t="s">
+        <v>412</v>
+      </c>
+      <c r="AJ183" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="184" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A184" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1999, 2010, 2020, </v>
-      </c>
-      <c r="AH183" s="37" t="s">
-        <v>412</v>
-      </c>
-      <c r="AI183" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="184" spans="1:35">
-      <c r="A184" s="20">
-        <f t="shared" si="6"/>
         <v>181</v>
       </c>
       <c r="B184" s="14" t="s">
@@ -37314,20 +37493,21 @@
       <c r="AD184" s="39"/>
       <c r="AE184" s="39"/>
       <c r="AF184" s="39"/>
-      <c r="AG184" s="12" t="str">
+      <c r="AG184" s="39"/>
+      <c r="AH184" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2001, 2010, 2020, </v>
+      </c>
+      <c r="AI184" s="37" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ184" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="185" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A185" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2001, 2010, 2020, </v>
-      </c>
-      <c r="AH184" s="37" t="s">
-        <v>413</v>
-      </c>
-      <c r="AI184" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="185" spans="1:35">
-      <c r="A185" s="20">
-        <f t="shared" si="6"/>
         <v>182</v>
       </c>
       <c r="B185" s="14" t="s">
@@ -37415,20 +37595,21 @@
       <c r="AD185" s="39"/>
       <c r="AE185" s="39"/>
       <c r="AF185" s="39"/>
-      <c r="AG185" s="12" t="str">
+      <c r="AG185" s="39"/>
+      <c r="AH185" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1999, 2010, 2020, </v>
+      </c>
+      <c r="AI185" s="37" t="s">
+        <v>414</v>
+      </c>
+      <c r="AJ185" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="186" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A186" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1999, 2010, 2020, </v>
-      </c>
-      <c r="AH185" s="37" t="s">
-        <v>414</v>
-      </c>
-      <c r="AI185" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="186" spans="1:35">
-      <c r="A186" s="20">
-        <f t="shared" si="6"/>
         <v>183</v>
       </c>
       <c r="B186" s="14" t="s">
@@ -37516,20 +37697,21 @@
       <c r="AD186" s="39"/>
       <c r="AE186" s="39"/>
       <c r="AF186" s="39"/>
-      <c r="AG186" s="12" t="str">
+      <c r="AG186" s="39"/>
+      <c r="AH186" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1999, 2010, 2020, </v>
+      </c>
+      <c r="AI186" s="37" t="s">
+        <v>415</v>
+      </c>
+      <c r="AJ186" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="187" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A187" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1999, 2010, 2020, </v>
-      </c>
-      <c r="AH186" s="37" t="s">
-        <v>415</v>
-      </c>
-      <c r="AI186" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="187" spans="1:35">
-      <c r="A187" s="20">
-        <f t="shared" si="6"/>
         <v>184</v>
       </c>
       <c r="B187" s="14" t="s">
@@ -37617,20 +37799,21 @@
       <c r="AD187" s="39"/>
       <c r="AE187" s="39"/>
       <c r="AF187" s="39"/>
-      <c r="AG187" s="12" t="str">
+      <c r="AG187" s="39"/>
+      <c r="AH187" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2002, 2012, 2017, </v>
+      </c>
+      <c r="AI187" s="37" t="s">
+        <v>416</v>
+      </c>
+      <c r="AJ187" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="188" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A188" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2002, 2012, 2017, </v>
-      </c>
-      <c r="AH187" s="37" t="s">
-        <v>416</v>
-      </c>
-      <c r="AI187" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="188" spans="1:35">
-      <c r="A188" s="20">
-        <f t="shared" si="6"/>
         <v>185</v>
       </c>
       <c r="B188" s="14" t="s">
@@ -37718,20 +37901,21 @@
       <c r="AD188" s="39"/>
       <c r="AE188" s="39"/>
       <c r="AF188" s="39"/>
-      <c r="AG188" s="12" t="str">
+      <c r="AG188" s="39"/>
+      <c r="AH188" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">1999, 2009, 2020, </v>
+      </c>
+      <c r="AI188" s="37" t="s">
+        <v>417</v>
+      </c>
+      <c r="AJ188" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="189" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A189" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">1999, 2009, 2020, </v>
-      </c>
-      <c r="AH188" s="37" t="s">
-        <v>417</v>
-      </c>
-      <c r="AI188" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="189" spans="1:35">
-      <c r="A189" s="20">
-        <f t="shared" si="6"/>
         <v>186</v>
       </c>
       <c r="B189" s="14" t="s">
@@ -37819,20 +38003,21 @@
       <c r="AD189" s="39"/>
       <c r="AE189" s="39"/>
       <c r="AF189" s="39"/>
-      <c r="AG189" s="12" t="str">
+      <c r="AG189" s="39"/>
+      <c r="AH189" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2000, </v>
+      </c>
+      <c r="AI189" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="AJ189" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="190" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A190" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2000, </v>
-      </c>
-      <c r="AH189" s="37" t="s">
-        <v>418</v>
-      </c>
-      <c r="AI189" s="42" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="190" spans="1:35">
-      <c r="A190" s="20">
-        <f t="shared" si="6"/>
         <v>187</v>
       </c>
       <c r="B190" s="14" t="s">
@@ -37922,20 +38107,21 @@
       </c>
       <c r="AE190" s="39"/>
       <c r="AF190" s="39"/>
-      <c r="AG190" s="12" t="str">
+      <c r="AG190" s="39"/>
+      <c r="AH190" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2022, </v>
+      </c>
+      <c r="AI190" s="37" t="s">
+        <v>419</v>
+      </c>
+      <c r="AJ190" s="9" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="191" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A191" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2022, </v>
-      </c>
-      <c r="AH190" s="37" t="s">
-        <v>419</v>
-      </c>
-      <c r="AI190" s="9" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="191" spans="1:35">
-      <c r="A191" s="20">
-        <f t="shared" si="6"/>
         <v>188</v>
       </c>
       <c r="B191" s="14" t="s">
@@ -38023,20 +38209,21 @@
       <c r="AD191" s="39"/>
       <c r="AE191" s="39"/>
       <c r="AF191" s="39"/>
-      <c r="AG191" s="12" t="str">
+      <c r="AG191" s="39"/>
+      <c r="AH191" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">2000, 2010, 2020, </v>
+      </c>
+      <c r="AI191" s="37" t="s">
+        <v>421</v>
+      </c>
+      <c r="AJ191" s="42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="192" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A192" s="20">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">2000, 2010, 2020, </v>
-      </c>
-      <c r="AH191" s="37" t="s">
-        <v>421</v>
-      </c>
-      <c r="AI191" s="42" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="192" spans="1:35">
-      <c r="A192" s="20">
-        <f t="shared" si="6"/>
         <v>189</v>
       </c>
       <c r="B192" s="14" t="s">
@@ -38124,20 +38311,21 @@
       <c r="AD192" s="39"/>
       <c r="AE192" s="39"/>
       <c r="AF192" s="39"/>
-      <c r="AG192" s="12" t="str">
-        <f>+IF($D192=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E192=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F192=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G192=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H192=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I192=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J192=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K192=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L192=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M192=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N192=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O192=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P192=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q192=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R192=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S192=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T192=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U192=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V192=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W192=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X192=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y192=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z192=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA192=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB192=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC192=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD192=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE192=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF192=1, RIGHT(AF$3,4)&amp;", ", "")</f>
+      <c r="AG192" s="39"/>
+      <c r="AH192" s="12" t="str">
+        <f t="shared" si="6"/>
         <v xml:space="preserve">1999, 2003, 2005, 2007, 2010, 2020, </v>
       </c>
-      <c r="AH192" s="37" t="s">
+      <c r="AI192" s="37" t="s">
         <v>422</v>
       </c>
-      <c r="AI192" s="42" t="s">
+      <c r="AJ192" s="42" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="193" spans="1:35">
+    <row r="193" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A193" s="20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>190</v>
       </c>
       <c r="B193" s="14" t="s">
@@ -38225,67 +38413,91 @@
       <c r="AD193" s="39"/>
       <c r="AE193" s="39"/>
       <c r="AF193" s="39"/>
-      <c r="AG193" s="12" t="str">
-        <f t="shared" si="5"/>
+      <c r="AG193" s="39"/>
+      <c r="AH193" s="12" t="str">
+        <f t="shared" si="6"/>
         <v xml:space="preserve">1997, 2002, 2007, 2012, 2017, </v>
       </c>
-      <c r="AH193" s="37" t="s">
+      <c r="AI193" s="37" t="s">
         <v>423</v>
       </c>
-      <c r="AI193" s="42" t="s">
+      <c r="AJ193" s="42" t="s">
         <v>229</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AJ40" r:id="rId1" xr:uid="{25E1DCAD-EDB6-45E1-AC63-4487170627B1}"/>
-    <hyperlink ref="AI158" r:id="rId2" xr:uid="{CB98B67B-85C7-4647-9CF2-CF8D96E194DF}"/>
-    <hyperlink ref="AI159:AI160" r:id="rId3" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{0FCB0F60-A15A-4866-AFFB-3823A7E93E1B}"/>
-    <hyperlink ref="AI161" r:id="rId4" xr:uid="{3226863B-ED15-4C03-948E-3248A1561225}"/>
-    <hyperlink ref="AI164" r:id="rId5" xr:uid="{2EBA3432-CC69-4AEF-8890-B4E60BE27490}"/>
-    <hyperlink ref="AI167" r:id="rId6" xr:uid="{6216BBE4-7EA8-43B5-B226-71498B2516E6}"/>
-    <hyperlink ref="AI170" r:id="rId7" xr:uid="{D36C98F0-6856-4284-BBD8-4AFB44229CD3}"/>
-    <hyperlink ref="AI173" r:id="rId8" xr:uid="{00DF0F23-BB56-46A4-9A24-F85E8E583DCD}"/>
-    <hyperlink ref="AI176" r:id="rId9" xr:uid="{6814D550-C28B-44FA-A08F-DBD3E4A9C09B}"/>
-    <hyperlink ref="AI179" r:id="rId10" xr:uid="{86EF9106-4CA3-43FB-B6E8-E7F5195DD18C}"/>
-    <hyperlink ref="AI182" r:id="rId11" xr:uid="{61DD2A63-CE73-4BE6-8772-8956F064E68F}"/>
-    <hyperlink ref="AI185" r:id="rId12" xr:uid="{CDADA14E-91B0-48F5-ABB0-AE99F6941082}"/>
-    <hyperlink ref="AI188" r:id="rId13" xr:uid="{4B7DA9CB-B68D-4FCB-9BDD-C649A454976F}"/>
-    <hyperlink ref="AI162:AI163" r:id="rId14" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{CB12E7EF-960C-47DE-8B5F-A91569A7DCC5}"/>
-    <hyperlink ref="AI165:AI166" r:id="rId15" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{7630AAF8-9A51-4444-9718-0720BA02D4BC}"/>
-    <hyperlink ref="AI168:AI169" r:id="rId16" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{6B4660FE-F8D8-4E1E-B06B-7422FA09CECB}"/>
-    <hyperlink ref="AI171:AI172" r:id="rId17" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{B3E5E7B5-AD90-47D8-A747-EFC35F97ECE1}"/>
-    <hyperlink ref="AI174:AI175" r:id="rId18" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{7FB817C6-382D-46C3-9045-776C66DA7FF6}"/>
-    <hyperlink ref="AI177:AI178" r:id="rId19" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{7EDEC8C8-157D-4F21-9AE7-BA90C2A1343C}"/>
-    <hyperlink ref="AI180:AI181" r:id="rId20" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{C21C8D5F-CAAE-47EC-88BC-3AD09D2DA2C3}"/>
-    <hyperlink ref="AI183:AI184" r:id="rId21" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{BBB2E8BD-499B-4A7F-9D78-122CC3F65905}"/>
-    <hyperlink ref="AI186:AI187" r:id="rId22" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{18184689-7C18-4C4E-A3AA-2B5CEFEA6DAE}"/>
-    <hyperlink ref="AI189" r:id="rId23" xr:uid="{568D2F46-FB34-476F-881F-BE909825A398}"/>
-    <hyperlink ref="AI191" r:id="rId24" xr:uid="{A101E863-14F7-4E60-8C22-DD69DC9B4AF9}"/>
-    <hyperlink ref="AI192" r:id="rId25" xr:uid="{A20238A4-08D4-4EAB-B328-85C6F817D923}"/>
-    <hyperlink ref="AI193" r:id="rId26" xr:uid="{A6B7ABF7-1120-4F6E-8759-2DAE6A23C483}"/>
-    <hyperlink ref="AI4" r:id="rId27" xr:uid="{07CC4A45-9030-4072-852C-25E8A1C00D15}"/>
-    <hyperlink ref="AI5:AI24" r:id="rId28" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{7CD24037-73B2-4F39-A0DE-ADD2B089D74B}"/>
-    <hyperlink ref="AI25" r:id="rId29" xr:uid="{478867AF-19F5-4812-A242-14764D7CE79C}"/>
-    <hyperlink ref="AI46" r:id="rId30" xr:uid="{DCC72901-C667-44BB-9599-DB8E1F71764F}"/>
-    <hyperlink ref="AI67" r:id="rId31" xr:uid="{35C44B32-3EF0-415C-9122-748F6CB9D753}"/>
-    <hyperlink ref="AI88" r:id="rId32" xr:uid="{876526C2-0616-4C3D-BF52-4658211F174D}"/>
-    <hyperlink ref="AI109" r:id="rId33" xr:uid="{7769B3EB-F1D5-49D7-B370-F49DF7E09EB3}"/>
-    <hyperlink ref="AI26:AI45" r:id="rId34" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{870E3DA2-B315-4C15-8A53-C48AC22D462D}"/>
-    <hyperlink ref="AI47:AI66" r:id="rId35" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{1266AA3D-7F68-44D8-B407-77279A492162}"/>
-    <hyperlink ref="AI68:AI87" r:id="rId36" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{954E7C6E-09CD-4421-B964-4359AC30D236}"/>
-    <hyperlink ref="AI89:AI108" r:id="rId37" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{41A64D13-5347-4A13-B529-9229C4EF7B60}"/>
-    <hyperlink ref="AI110:AI112" r:id="rId38" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{5A74E1F5-3AF2-4FD9-99F6-7EF0A8DC87AB}"/>
-    <hyperlink ref="AI114" r:id="rId39" xr:uid="{BD56FD01-D644-424F-A0F2-994F4D01C828}"/>
-    <hyperlink ref="AI115:AI157" r:id="rId40" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{DD95001C-7C20-44FA-B989-9B9CD176213A}"/>
+    <hyperlink ref="AK40" r:id="rId1" xr:uid="{25E1DCAD-EDB6-45E1-AC63-4487170627B1}"/>
+    <hyperlink ref="AJ158" r:id="rId2" xr:uid="{CB98B67B-85C7-4647-9CF2-CF8D96E194DF}"/>
+    <hyperlink ref="AJ159:AJ160" r:id="rId3" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{0FCB0F60-A15A-4866-AFFB-3823A7E93E1B}"/>
+    <hyperlink ref="AJ161" r:id="rId4" xr:uid="{3226863B-ED15-4C03-948E-3248A1561225}"/>
+    <hyperlink ref="AJ164" r:id="rId5" xr:uid="{2EBA3432-CC69-4AEF-8890-B4E60BE27490}"/>
+    <hyperlink ref="AJ167" r:id="rId6" xr:uid="{6216BBE4-7EA8-43B5-B226-71498B2516E6}"/>
+    <hyperlink ref="AJ170" r:id="rId7" xr:uid="{D36C98F0-6856-4284-BBD8-4AFB44229CD3}"/>
+    <hyperlink ref="AJ173" r:id="rId8" xr:uid="{00DF0F23-BB56-46A4-9A24-F85E8E583DCD}"/>
+    <hyperlink ref="AJ176" r:id="rId9" xr:uid="{6814D550-C28B-44FA-A08F-DBD3E4A9C09B}"/>
+    <hyperlink ref="AJ179" r:id="rId10" xr:uid="{86EF9106-4CA3-43FB-B6E8-E7F5195DD18C}"/>
+    <hyperlink ref="AJ182" r:id="rId11" xr:uid="{61DD2A63-CE73-4BE6-8772-8956F064E68F}"/>
+    <hyperlink ref="AJ185" r:id="rId12" xr:uid="{CDADA14E-91B0-48F5-ABB0-AE99F6941082}"/>
+    <hyperlink ref="AJ188" r:id="rId13" xr:uid="{4B7DA9CB-B68D-4FCB-9BDD-C649A454976F}"/>
+    <hyperlink ref="AJ162:AJ163" r:id="rId14" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{CB12E7EF-960C-47DE-8B5F-A91569A7DCC5}"/>
+    <hyperlink ref="AJ165:AJ166" r:id="rId15" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{7630AAF8-9A51-4444-9718-0720BA02D4BC}"/>
+    <hyperlink ref="AJ168:AJ169" r:id="rId16" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{6B4660FE-F8D8-4E1E-B06B-7422FA09CECB}"/>
+    <hyperlink ref="AJ171:AJ172" r:id="rId17" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{B3E5E7B5-AD90-47D8-A747-EFC35F97ECE1}"/>
+    <hyperlink ref="AJ174:AJ175" r:id="rId18" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{7FB817C6-382D-46C3-9045-776C66DA7FF6}"/>
+    <hyperlink ref="AJ177:AJ178" r:id="rId19" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{7EDEC8C8-157D-4F21-9AE7-BA90C2A1343C}"/>
+    <hyperlink ref="AJ180:AJ181" r:id="rId20" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{C21C8D5F-CAAE-47EC-88BC-3AD09D2DA2C3}"/>
+    <hyperlink ref="AJ183:AJ184" r:id="rId21" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{BBB2E8BD-499B-4A7F-9D78-122CC3F65905}"/>
+    <hyperlink ref="AJ186:AJ187" r:id="rId22" display="https://www.fao.org/world-census-agriculture/wca-round/wca-round-2020/en" xr:uid="{18184689-7C18-4C4E-A3AA-2B5CEFEA6DAE}"/>
+    <hyperlink ref="AJ189" r:id="rId23" xr:uid="{568D2F46-FB34-476F-881F-BE909825A398}"/>
+    <hyperlink ref="AJ191" r:id="rId24" xr:uid="{A101E863-14F7-4E60-8C22-DD69DC9B4AF9}"/>
+    <hyperlink ref="AJ192" r:id="rId25" xr:uid="{A20238A4-08D4-4EAB-B328-85C6F817D923}"/>
+    <hyperlink ref="AJ193" r:id="rId26" xr:uid="{A6B7ABF7-1120-4F6E-8759-2DAE6A23C483}"/>
+    <hyperlink ref="AJ4" r:id="rId27" xr:uid="{07CC4A45-9030-4072-852C-25E8A1C00D15}"/>
+    <hyperlink ref="AJ5:AJ24" r:id="rId28" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{7CD24037-73B2-4F39-A0DE-ADD2B089D74B}"/>
+    <hyperlink ref="AJ25" r:id="rId29" xr:uid="{478867AF-19F5-4812-A242-14764D7CE79C}"/>
+    <hyperlink ref="AJ46" r:id="rId30" xr:uid="{DCC72901-C667-44BB-9599-DB8E1F71764F}"/>
+    <hyperlink ref="AJ67" r:id="rId31" xr:uid="{35C44B32-3EF0-415C-9122-748F6CB9D753}"/>
+    <hyperlink ref="AJ88" r:id="rId32" xr:uid="{876526C2-0616-4C3D-BF52-4658211F174D}"/>
+    <hyperlink ref="AJ109" r:id="rId33" xr:uid="{7769B3EB-F1D5-49D7-B370-F49DF7E09EB3}"/>
+    <hyperlink ref="AJ26:AJ45" r:id="rId34" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{870E3DA2-B315-4C15-8A53-C48AC22D462D}"/>
+    <hyperlink ref="AJ47:AJ66" r:id="rId35" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{1266AA3D-7F68-44D8-B407-77279A492162}"/>
+    <hyperlink ref="AJ68:AJ87" r:id="rId36" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{954E7C6E-09CD-4421-B964-4359AC30D236}"/>
+    <hyperlink ref="AJ89:AJ108" r:id="rId37" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{41A64D13-5347-4A13-B529-9229C4EF7B60}"/>
+    <hyperlink ref="AJ110:AJ112" r:id="rId38" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{5A74E1F5-3AF2-4FD9-99F6-7EF0A8DC87AB}"/>
+    <hyperlink ref="AJ114" r:id="rId39" xr:uid="{BD56FD01-D644-424F-A0F2-994F4D01C828}"/>
+    <hyperlink ref="AJ115:AJ157" r:id="rId40" display="https://www.fao.org/world-census-agriculture/wcarounds/wca2020/countries2020/en/" xr:uid="{DD95001C-7C20-44FA-B989-9B9CD176213A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId41"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Official Use Only</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId42"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3e02667f-0271-471b-bd6e-11a2e16def1d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b19ad29f-88fa-4d62-ac16-34b992563bf9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ADB9CD767C4FF34281D6635032C5B89D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3b7ad1acb7d07f4c67b79ea712f2c443">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b19ad29f-88fa-4d62-ac16-34b992563bf9" xmlns:ns3="e781ea9d-1795-4792-8d8d-c86ae526af93" xmlns:ns4="3e02667f-0271-471b-bd6e-11a2e16def1d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e0bd56705adf4bb69ae57d53dbdc9cd2" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
@@ -38533,34 +38745,48 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3e02667f-0271-471b-bd6e-11a2e16def1d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b19ad29f-88fa-4d62-ac16-34b992563bf9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C0FE447-6A59-456A-9424-0DEFE930C294}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C096552-319F-494A-92C1-A84ED14A1FEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="e781ea9d-1795-4792-8d8d-c86ae526af93"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="3e02667f-0271-471b-bd6e-11a2e16def1d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26BEC7CC-A89E-4B59-A350-12F5A7982677}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26BEC7CC-A89E-4B59-A350-12F5A7982677}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C096552-319F-494A-92C1-A84ED14A1FEF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C0FE447-6A59-456A-9424-0DEFE930C294}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
+    <ds:schemaRef ds:uri="e781ea9d-1795-4792-8d8d-c86ae526af93"/>
+    <ds:schemaRef ds:uri="3e02667f-0271-471b-bd6e-11a2e16def1d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>